--- a/data/credit_bond_all_2026-09-02.xlsx
+++ b/data/credit_bond_all_2026-09-02.xlsx
@@ -957,8 +957,12 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>41.61</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.90</t>
@@ -1014,8 +1018,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
           <t>6-</t>
@@ -1149,9 +1157,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1185,8 +1191,12 @@
           <t>1.75 ~ 2.10</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>45.61</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.82</t>
@@ -1242,8 +1252,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1377,9 +1391,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ5" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ5" s="3"/>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
@@ -1413,8 +1425,12 @@
           <t>1.70 ~ 2.30</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>56.61</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -1470,8 +1486,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>3.17</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1605,9 +1625,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ6" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ6" s="3"/>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
@@ -2755,8 +2773,12 @@
           <t>1.71 ~ 1.91</t>
         </is>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>67.41</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -2962,7 +2984,11 @@
           <t>09-02 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>032680509.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -7357,8 +7383,12 @@
           <t>1.60 ~ 2.20</t>
         </is>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="H32" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>22.61</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>1.97</t>
@@ -7410,8 +7440,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+      <c r="U32" s="4" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>2.08</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -7583,8 +7617,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="H33" s="4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>34.47</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -7640,8 +7678,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+      <c r="U33" s="4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>1.375</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -7802,15 +7844,19 @@
         <v>2.5</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="H34" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>44.47</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -7866,8 +7912,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1.71</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -8450,72 +8500,74 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26菏财GT02</t>
+          <t>26中交租赁SCP005</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>520446.SZ</t>
+          <t>012682196.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2.21</v>
+        <v>1.44</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>80.61</v>
+        <v>17.12</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25菏财04</t>
+          <t>24交租V1</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.25Y</t>
+          <t>278D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2.1338</t>
+          <t>1.5683</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2.1300/2.1300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>菏泽财金投资集团有限公司</t>
+          <t>中交融资租赁有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B 51.88</t>
+          <t>C- 12.63</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8525,7 +8577,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8535,117 +8587,121 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>3.3833</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.53%~1.57%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>山东省-菏泽市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期超短期融资券拟募集资金6亿元,拟全部用于偿还发行人即将到期的债务融资工具[26中交租赁SCP003]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>上海银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>菏泽财金投资集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)(品种二)</t>
+          <t>中交融资租赁有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8678,7 +8734,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26曹国07</t>
+          <t>26菏财GT02</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8688,62 +8744,62 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>245951.SH</t>
+          <t>520446.SZ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>62.72</v>
+        <v>80.61</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>24曹妃国控MTN004</t>
+          <t>25菏财04</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.25Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.9241</t>
+          <t>2.1338</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1300/2.1300</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司</t>
+          <t>菏泽财金投资集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.61</t>
+          <t>B 51.88</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8775,32 +8831,28 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>山东省-菏泽市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
+          <t>国投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -8816,22 +8868,22 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
+          <t>菏泽财金投资集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
@@ -8852,7 +8904,7 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
@@ -8862,22 +8914,22 @@
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8910,7 +8962,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26深投08</t>
+          <t>26曹国07</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8920,12 +8972,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>524988.SZ</t>
+          <t>245951.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -8934,48 +8986,48 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>39.39</v>
+        <v>62.72</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26深投控MTN004B</t>
+          <t>24曹妃国控MTN004</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>9.89Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.1167</t>
+          <t>1.9241</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>2.1300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司</t>
+          <t>曹妃甸国控投资集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 23.98</t>
+          <t>C+ 34.61</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8995,19 +9047,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9022,17 +9074,17 @@
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -9048,12 +9100,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
+          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9063,14 +9115,10 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2036-09-07</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-04</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9083,7 +9131,7 @@
       </c>
       <c r="AN39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AO39" s="3" t="inlineStr">
@@ -9093,7 +9141,7 @@
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
@@ -9103,12 +9151,12 @@
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
@@ -9146,68 +9194,72 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26临平交通PPN004</t>
+          <t>26深投08</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
-        </is>
-      </c>
-      <c r="C40" s="3"/>
+          <t>09-02 19:00</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>524988.SZ</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>34.61</v>
+        <v>39.39</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26临交01</t>
+          <t>26深投控MTN004B</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+2.00Y</t>
+          <t>9.89Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.7538</t>
+          <t>2.1167</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>2.1300/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>杭州临平交通集团有限公司</t>
+          <t>深圳市投资控股有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 40.33</t>
+          <t>C- 23.98</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9217,7 +9269,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9227,50 +9279,50 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U40" s="4" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>1.25</v>
-      </c>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z40" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额人民币10亿元,拟用于偿还发行人本部有息债务[23临平交通PPN003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,兴业银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司</t>
+          <t>国信证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9280,48 +9332,52 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>杭州临平交通集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2036-09-07</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AM40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
@@ -9331,12 +9387,12 @@
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
@@ -9346,7 +9402,7 @@
       </c>
       <c r="AU40" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV40" s="3" t="inlineStr">
@@ -9356,7 +9412,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9374,70 +9430,68 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26嘉善国控MTN005</t>
+          <t>26临平交通PPN004</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>102683521.IB</t>
-        </is>
-      </c>
+          <t>09-02 18:00</t>
+        </is>
+      </c>
+      <c r="C41" s="3"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>34.61</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26嘉善国控MTN004</t>
+          <t>26临交01</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.88Y</t>
+          <t>2.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.8436</t>
+          <t>1.7538</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.8350/1.8300</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>嘉善县国创资本控股集团有限公司</t>
+          <t>杭州临平交通集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 46.44</t>
+          <t>B- 40.33</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9460,43 +9514,47 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
+      <c r="U41" s="4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行规模7亿元,募集资金用于偿还发行人下属子公司存量债务融资工具本金。[23嘉善国投PPN004]</t>
+          <t>本期发行金额人民币10亿元,拟用于偿还发行人本部有息债务[23临平交通PPN003]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,杭州银行股份有限公司</t>
+          <t>宁波银行股份有限公司,兴业银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9511,12 +9569,12 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>嘉善县国创资本控股集团有限公司2026年度第五期中期票据</t>
+          <t>杭州临平交通集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
@@ -9532,7 +9590,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
@@ -9542,7 +9600,7 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
@@ -9572,7 +9630,7 @@
       </c>
       <c r="AU41" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV41" s="3" t="inlineStr">
@@ -9582,7 +9640,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9592,7 +9650,7 @@
       </c>
       <c r="AY41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ41" s="3"/>
@@ -9600,74 +9658,74 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26渤海银行债01</t>
+          <t>26嘉善国控MTN005</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>09-02 17:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>212680029.IB</t>
+          <t>102683521.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>100.0</v>
+        <v>7.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>150.0</v>
+        <v>7.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>34.72</v>
+        <v>34.61</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25渤海银行债02A</t>
+          <t>26嘉善国控MTN004</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>4.88Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.6002</t>
+          <t>1.8436</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.6100/--</t>
+          <t>1.8350/1.8300</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>嘉善县国创资本控股集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>A 74.40</t>
+          <t>B- 46.44</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9690,8 +9748,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
+      <c r="U42" s="4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>1.43</v>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -9699,7 +9761,7 @@
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -9707,30 +9769,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源 ，优化负债期限结构 ，促进业务的稳健发展 。</t>
+          <t>发行人本期中期票据发行规模7亿元,募集资金用于偿还发行人下属子公司存量债务融资工具本金。[23嘉善国投PPN004]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,华夏银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,国投证券股份有限公司,国开证券股份有限公司,东方证券股份有限公司</t>
+          <t>宁波银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9745,7 +9803,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司2026年金融债券(第一期)</t>
+          <t>嘉善县国创资本控股集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9755,60 +9813,60 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AO42" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ42" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR42" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>股份制银行</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9826,7 +9884,7 @@
       </c>
       <c r="AY42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AZ42" s="3"/>
@@ -9834,72 +9892,74 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26怀科01</t>
+          <t>26渤海银行债01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 17:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283753.SH</t>
+          <t>212680029.IB</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>100.0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>150.0</v>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>37.61</v>
+        <v>34.72</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26怀柔科学PPN002</t>
+          <t>25渤海银行债02A</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+2.00Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7591</t>
+          <t>1.6002</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C 26.96</t>
+          <t>A 74.40</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9909,7 +9969,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -9926,12 +9986,12 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -9946,23 +10006,23 @@
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>北京市-怀柔区</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于偿还到期的公司债券[23怀科01]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源 ，优化负债期限结构 ，促进业务的稳健发展 。</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,华夏银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,国投证券股份有限公司,国开证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -9972,22 +10032,22 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>渤海银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
@@ -9998,7 +10058,7 @@
       </c>
       <c r="AM43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN43" s="3" t="inlineStr">
@@ -10008,37 +10068,37 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -10048,7 +10108,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -10066,7 +10126,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26沂投03</t>
+          <t>26怀科01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10076,64 +10136,62 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283864.SH</t>
+          <t>283753.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>5.9</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>57.72</v>
+        <v>37.61</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26沂投02</t>
+          <t>26怀柔科学PPN002</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>2.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.8701</t>
+          <t>1.7591</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>1.8900/1.8700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>新沂市城市投资发展集团有限公司</t>
+          <t>北京怀柔科学城建设发展有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C 28.88</t>
+          <t>C 26.96</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10143,7 +10201,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10153,49 +10211,47 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="n">
-        <v>4.1525</v>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z44" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>北京市-怀柔区</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23沂投05]</t>
+          <t>本期公司债券募集资金拟用于偿还到期的公司债券[23怀科01]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,天风证券股份有限公司,国投证券股份有限公司,南京证券股份有限公司,兴业证券股份有限公司,东兴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD44" s="3" t="inlineStr">
-        <is>
-          <t>江苏钟吾城乡投资发展集团有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10213,7 +10269,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>新沂市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10223,7 +10279,7 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
@@ -10239,32 +10295,32 @@
       </c>
       <c r="AN44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
@@ -10274,17 +10330,17 @@
       </c>
       <c r="AU44" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10302,7 +10358,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26蓉产02</t>
+          <t>26沂投03</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10312,62 +10368,64 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>524985.SZ</t>
+          <t>283864.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F45" s="3"/>
+        <v>5.9</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>5.9</v>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>-0.61</v>
+        <v>57.72</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26成都产投MTN003</t>
+          <t>26沂投02</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4.92Y+5.00Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.8002</t>
+          <t>1.8701</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8900/1.8700</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>成都产业投资集团有限公司</t>
+          <t>新沂市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.69</t>
+          <t>C 28.88</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10387,45 +10445,49 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>6.38</v>
+        <v>4.1525</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟募集资金不超过10.00亿元(含10.00亿元),扣除发行费用后,拟用于生产性支出,具体包括偿还到期债务以及相关适用法律法规及/或监管机构允许的用途,具体用途根据公司资金需求情况确定。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23沂投05]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国国际金融股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD45" s="3"/>
+          <t>国金证券股份有限公司,天风证券股份有限公司,国投证券股份有限公司,南京证券股份有限公司,兴业证券股份有限公司,东兴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr">
+        <is>
+          <t>江苏钟吾城乡投资发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE45" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10438,22 +10500,22 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>成都产业投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>新沂市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2036-09-04</t>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10464,22 +10526,22 @@
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
@@ -10489,32 +10551,32 @@
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -10532,7 +10594,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26珠华04</t>
+          <t>26蓉产02</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10542,47 +10604,47 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>520444.SZ</t>
+          <t>524985.SZ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>2+2+1</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>134.61</v>
+        <v>-0.61</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>25珠华02</t>
+          <t>26成都产投MTN003</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2.21Y+2.00Y</t>
+          <t>4.92Y+5.00Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2.8118</t>
+          <t>1.8002</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -10592,12 +10654,12 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>成都产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>B- 37.49</t>
+          <t>C+ 30.69</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10620,16 +10682,18 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U46" s="3"/>
+      <c r="U46" s="4" t="n">
+        <v>6.38</v>
+      </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>2.73%~2.83%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10640,17 +10704,17 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于置换到期的公司债券本金[23珠华Y3]</t>
+          <t>本期公司债券拟募集资金不超过10.00亿元(含10.00亿元),扣除发行费用后,拟用于生产性支出,具体包括偿还到期债务以及相关适用法律法规及/或监管机构允许的用途,具体用途根据公司资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司,国泰海通证券股份有限公司,西部证券股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,国信证券股份有限公司,中国银河证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>国金证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
@@ -10671,17 +10735,17 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>成都产业投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2036-09-04</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
@@ -10692,7 +10756,7 @@
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN46" s="3" t="inlineStr">
@@ -10707,7 +10771,7 @@
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
@@ -10732,7 +10796,7 @@
       </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AV46" s="3" t="inlineStr">
@@ -10760,7 +10824,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26曹国08</t>
+          <t>26珠华04</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10770,12 +10834,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>245952.SH</t>
+          <t>520444.SZ</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2+2+1</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
@@ -10784,48 +10848,48 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>2.07</v>
+        <v>2.75</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>66.61</v>
+        <v>134.61</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26曹妃国控MTN003B</t>
+          <t>25珠华02</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>4.62Y</t>
+          <t>2.21Y+2.00Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>2.1430</t>
+          <t>2.8118</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>2.1400/2.1200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.61</t>
+          <t>B- 37.49</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10852,12 +10916,12 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>2.73%~2.83%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -10865,24 +10929,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z47" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于置换到期的公司债券本金[23珠华Y3]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
+          <t>华金证券股份有限公司,国泰海通证券股份有限公司,西部证券股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,国信证券股份有限公司,中国银河证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10898,17 +10958,17 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
+          <t>珠海华发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
@@ -10924,7 +10984,7 @@
       </c>
       <c r="AM47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN47" s="3" t="inlineStr">
@@ -10939,7 +10999,7 @@
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
@@ -10949,12 +11009,12 @@
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
@@ -10964,7 +11024,7 @@
       </c>
       <c r="AU47" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AV47" s="3" t="inlineStr">
@@ -10974,7 +11034,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">
@@ -10992,7 +11052,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>赣投YK08</t>
+          <t>26曹国08</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -11002,62 +11062,62 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>245982.SH</t>
+          <t>245952.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>37.72</v>
+        <v>66.61</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>赣投YK04</t>
+          <t>26曹妃国控MTN003B</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.86Y+N</t>
+          <t>4.62Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.6882</t>
+          <t>2.1430</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.6950</t>
+          <t>2.1400/2.1200</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>江西省投资集团有限公司</t>
+          <t>曹妃甸国控投资集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B- 37.52</t>
+          <t>C+ 34.61</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11067,7 +11127,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -11084,12 +11144,12 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -11097,20 +11157,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z48" s="3"/>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>江西省</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过15.00亿元,扣除相关发行费用后拟将不超过10.00亿元偿还到期公司债券本金;不超过5.00亿元偿还有息债务。[赣投YK01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司,广发证券股份有限公司</t>
+          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
@@ -11131,7 +11195,7 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>江西省投资集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第三期)</t>
+          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11141,7 +11205,7 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
@@ -11152,7 +11216,7 @@
       </c>
       <c r="AM48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN48" s="3" t="inlineStr">
@@ -11167,7 +11231,7 @@
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
@@ -11177,17 +11241,17 @@
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -11202,7 +11266,7 @@
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">
@@ -11220,37 +11284,39 @@
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26酒钢MTN003</t>
+          <t>赣投YK08</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>102683525.IB</t>
+          <t>245982.SH</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>15.0</v>
+      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>37.72</v>
+      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -11258,32 +11324,32 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>25酒钢MTN001(科创债)</t>
+          <t>赣投YK04</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2.06Y</t>
+          <t>2.86Y+N</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.8257</t>
+          <t>1.6882</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/1.6950</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>酒泉钢铁(集团)有限责任公司</t>
+          <t>江西省投资集团有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>C- 21.00</t>
+          <t>B- 37.52</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11293,7 +11359,7 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -11310,12 +11376,12 @@
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
@@ -11326,23 +11392,23 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>甘肃省-嘉峪关市</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>本期永续中期票据发行拟募集资金5亿元,所募集资金拟用于归还金融机构贷款及支付氧化铝货款。</t>
+          <t>本期债券发行规模为不超过15.00亿元,扣除相关发行费用后拟将不超过10.00亿元偿还到期公司债券本金;不超过5.00亿元偿还有息债务。[赣投YK01]</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,东兴证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
@@ -11352,12 +11418,12 @@
       </c>
       <c r="AG49" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>酒泉钢铁(集团)有限责任公司2026年度第三期中期票据</t>
+          <t>江西省投资集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11367,18 +11433,18 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN49" s="3" t="inlineStr">
@@ -11393,27 +11459,27 @@
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11433,37 +11499,35 @@
       </c>
       <c r="AX49" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AZ49" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AZ49" s="3"/>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26振华重工SCP002(蓝债)</t>
+          <t>26酒钢MTN003</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>012682195.IB</t>
+          <t>102683525.IB</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -11474,33 +11538,33 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.70 ~ 2.20</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>15.84</v>
+        <v>61.41</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>26振华重工SCP001(绿色)</t>
+          <t>25酒钢MTN001(科创债)</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>181D</t>
+          <t>2.06Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.5110</t>
+          <t>1.8257</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -11510,12 +11574,12 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>上海振华重工(集团)股份有限公司</t>
+          <t>酒泉钢铁(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>D- 1.59</t>
+          <t>C- 21.00</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11535,23 +11599,23 @@
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>4.64</v>
+        <v>2.64</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>4.41</v>
+        <v>3.25</v>
       </c>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -11562,28 +11626,28 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>甘肃省-嘉峪关市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟发行金额为5.00亿元,募集资金将全部用于置换发行前三个月内,发行人在符合一级能效的节能岸边集装箱起重机制造项目中,用于原材料采购、生产制造等环节的自有资金支出。本次置换出的发行人自有资金拟用于补充发行人流动资金。</t>
+          <t>本期永续中期票据发行拟募集资金5亿元,所募集资金拟用于归还金融机构贷款及支付氧化铝货款。</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr">
@@ -11593,7 +11657,7 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>上海振华重工(集团)股份有限公司2026年度第二期绿色超短期融资券(蓝色债券)</t>
+          <t>酒泉钢铁(集团)有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
@@ -11603,82 +11667,78 @@
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2027-04-03</t>
-        </is>
-      </c>
-      <c r="AK50" s="3" t="inlineStr">
-        <is>
-          <t>休3</t>
-        </is>
-      </c>
+          <t>2028-09-04</t>
+        </is>
+      </c>
+      <c r="AK50" s="3"/>
       <c r="AL50" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AM50" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AN50" s="3" t="inlineStr">
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>普钢</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>次级债权</t>
+        </is>
+      </c>
+      <c r="AY50" s="3" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AO50" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ50" s="3" t="inlineStr">
-        <is>
-          <t>其他设备制造</t>
-        </is>
-      </c>
-      <c r="AR50" s="3" t="inlineStr">
-        <is>
-          <t>其他专用设备</t>
-        </is>
-      </c>
-      <c r="AS50" s="3" t="inlineStr">
-        <is>
-          <t>其他专用设备</t>
-        </is>
-      </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
-          <t>专用设备</t>
-        </is>
-      </c>
-      <c r="AU50" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV50" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW50" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX50" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ50" s="3"/>
@@ -11686,7 +11746,7 @@
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26河钢集MTN018</t>
+          <t>26振华重工SCP002(蓝债)</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11696,64 +11756,64 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>102683533.IB</t>
+          <t>012682195.IB</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.78</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>52.72</v>
+        <v>15.84</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>26河钢集MTN017A</t>
+          <t>26振华重工SCP001(绿色)</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2.85Y</t>
+          <t>181D</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.7970</t>
+          <t>1.5110</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>1.8100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>河钢集团有限公司</t>
+          <t>上海振华重工(集团)股份有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>B- 36.84</t>
+          <t>D- 1.59</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11776,16 +11836,20 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
+      <c r="U51" s="4" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="V51" s="4" t="n">
+        <v>4.41</v>
+      </c>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
@@ -11796,28 +11860,28 @@
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为10亿元,募集资金拟用于偿还发行人及其子公司即将到期的有息债务,补充发行人及其子公司日常运营周转</t>
+          <t>本期债券拟发行金额为5.00亿元,募集资金将全部用于置换发行前三个月内,发行人在符合一级能效的节能岸边集装箱起重机制造项目中,用于原材料采购、生产制造等环节的自有资金支出。本次置换出的发行人自有资金拟用于补充发行人流动资金。</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>渤海银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG51" s="3" t="inlineStr">
@@ -11827,7 +11891,7 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>河钢集团有限公司2026年度第十八期中期票据</t>
+          <t>上海振华重工(集团)股份有限公司2026年度第二期绿色超短期融资券(蓝色债券)</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -11837,10 +11901,14 @@
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
-        </is>
-      </c>
-      <c r="AK51" s="3"/>
+          <t>2027-04-03</t>
+        </is>
+      </c>
+      <c r="AK51" s="3" t="inlineStr">
+        <is>
+          <t>休3</t>
+        </is>
+      </c>
       <c r="AL51" s="3" t="inlineStr">
         <is>
           <t>2026-09-04</t>
@@ -11848,7 +11916,7 @@
       </c>
       <c r="AM51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN51" s="3" t="inlineStr">
@@ -11863,27 +11931,27 @@
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>其他设备制造</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>其他专用设备</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>其他专用设备</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>专用设备</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -11911,14 +11979,12 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AZ51" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ51" s="3"/>
     </row>
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26鄂能源SCP008</t>
+          <t>26河钢集MTN018</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -11928,12 +11994,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>012682200.IB</t>
+          <t>102683533.IB</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
@@ -11944,48 +12010,48 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.60</t>
+          <t>1.50 ~ 1.78</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>20.12</v>
+        <v>52.72</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26鄂能源SCP007</t>
+          <t>26河钢集MTN017A</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>41D</t>
+          <t>2.85Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.4727</t>
+          <t>1.7970</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8100/--</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>湖北能源集团股份有限公司</t>
+          <t>河钢集团有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.00</t>
+          <t>B- 36.84</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12009,19 +12075,17 @@
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="V52" s="4" t="n">
-        <v>1.08</v>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -12032,28 +12096,28 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额10亿元,全部用于发行人及子公司偿还有息债务本息。</t>
+          <t>本期中期票据发行规模为10亿元,募集资金拟用于偿还发行人及其子公司即将到期的有息债务,补充发行人及其子公司日常运营周转</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG52" s="3" t="inlineStr">
@@ -12063,7 +12127,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>湖北能源集团股份有限公司2026年度第八期超短期融资券</t>
+          <t>河钢集团有限公司2026年度第十八期中期票据</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12073,7 +12137,7 @@
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AK52" s="3"/>
@@ -12104,22 +12168,22 @@
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12147,12 +12211,14 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="AZ52" s="3"/>
+      <c r="AZ52" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26象屿融租MTN001(绿色)</t>
+          <t>26鄂能源SCP008</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -12162,49 +12228,49 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>102683515.IB</t>
+          <t>012682200.IB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.45</t>
+          <t>1.35 ~ 1.60</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>102.61</v>
+        <v>20.12</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>25兴泰租赁MTN002</t>
+          <t>26鄂能源SCP007</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>1.37Y</t>
+          <t>41D</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.7996</t>
+          <t>1.4727</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -12214,12 +12280,12 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>厦门象屿金象融资租赁有限公司</t>
+          <t>湖北能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C+ 34.00</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12243,59 +12309,51 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>1.25</v>
+        <v>3.63</v>
       </c>
       <c r="V53" s="4" t="n">
-        <v>1.0</v>
+        <v>1.08</v>
       </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>2.06%~2.16%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z53" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>发行人拟使用本次绿色中期票据【2】亿元用于偿还发行人及下属子公司金融机构借款；本期债券募集资金拟投放大同市浑源县亨源洪独立储能项目20000万元用于偿还银行借款</t>
+          <t>本期超短期融资券发行金额10亿元,全部用于发行人及子公司偿还有息债务本息。</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司,广东南海农村商业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD53" s="3" t="inlineStr">
-        <is>
-          <t>厦门象屿金象控股集团有限公司</t>
-        </is>
-      </c>
+          <t>上海浦东发展银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG53" s="3" t="inlineStr">
@@ -12305,7 +12363,7 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>厦门象屿金象融资租赁有限公司2026年度第一期绿色中期票据</t>
+          <t>湖北能源集团股份有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12315,7 +12373,7 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2031-09-03</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="AK53" s="3"/>
@@ -12326,7 +12384,7 @@
       </c>
       <c r="AM53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN53" s="3" t="inlineStr">
@@ -12336,32 +12394,32 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
@@ -12371,7 +12429,7 @@
       </c>
       <c r="AV53" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW53" s="3" t="inlineStr">
@@ -12394,7 +12452,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26中交租赁SCP005</t>
+          <t>26象屿融租MTN001(绿色)</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12404,64 +12462,64 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>012682196.IB</t>
+          <t>102683515.IB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>2.00 ~ 2.45</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1.44</v>
+        <v>2.43</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>17.12</v>
+        <v>102.61</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>24交租V1</t>
+          <t>25兴泰租赁MTN002</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>278D</t>
+          <t>1.37Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.5683</t>
+          <t>1.7996</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>中交融资租赁有限公司</t>
+          <t>厦门象屿金象融资租赁有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C- 12.63</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12485,51 +12543,59 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>3.38</v>
+        <v>1.25</v>
       </c>
       <c r="V54" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.57%</t>
+          <t>2.06%~2.16%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金6亿元,拟全部用于偿还发行人即将到期的债务融资工具[26中交租赁SCP003]</t>
+          <t>发行人拟使用本次绿色中期票据【2】亿元用于偿还发行人及下属子公司金融机构借款；本期债券募集资金拟投放大同市浑源县亨源洪独立储能项目20000万元用于偿还银行借款</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD54" s="3"/>
+          <t>浙商银行股份有限公司,广东南海农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr">
+        <is>
+          <t>厦门象屿金象控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE54" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF54" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG54" s="3" t="inlineStr">
@@ -12539,7 +12605,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>中交融资租赁有限公司2026年度第五期超短期融资券</t>
+          <t>厦门象屿金象融资租赁有限公司2026年度第一期绿色中期票据</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12549,7 +12615,7 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2031-09-03</t>
         </is>
       </c>
       <c r="AK54" s="3"/>
@@ -12575,7 +12641,7 @@
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
@@ -12605,7 +12671,7 @@
       </c>
       <c r="AV54" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW54" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-02.xlsx
+++ b/data/credit_bond_all_2026-09-02.xlsx
@@ -2988,7 +2988,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26南海农商行绿债01A</t>
+          <t>26科学城MTN006(项目收益)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2998,64 +2998,64 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>222680019.IB</t>
+          <t>102683532.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+3+3+3+3</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>37.72</v>
+        <v>-27.24</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>25南海农商行债01</t>
+          <t>24科学城MTN002(项目收益)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>3.01Y+4.00Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6179</t>
+          <t>1.7045</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.6300/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>广东南海农村商业银行股份有限公司</t>
+          <t>北京未来科学城发展集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.87</t>
+          <t>C- 18.56</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3075,19 +3075,21 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U13" s="3"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>4.6333</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3095,35 +3097,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>北京市-昌平区</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行规模不超过8亿元人民币的绿色金融债券,募集资金拟投向符合《绿色金融支持项目目录(2025年版)》标准的绿色储备项目共9项,项目拟使用绿色债券募集资金8.40亿元人民币。</t>
+          <t>本次债券的募集资金扣除发行费用后,拟用于偿还到期中期票据(项目收益)[21科学城MTN003B(项目收益)]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
@@ -3133,7 +3131,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>广东南海农村商业银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
+          <t>北京未来科学城发展集团有限公司2026年度第六期中期票据(项目收益)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3143,28 +3141,28 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2041-09-03</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
@@ -3174,27 +3172,27 @@
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3204,7 +3202,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3222,7 +3220,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26科学城MTN006(项目收益)</t>
+          <t>26苏元禾MTN002B(科创债)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3232,64 +3230,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683532.IB</t>
+          <t>102683476.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3+3+3+3+3</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.61 ~ 1.91</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
         <v>1.7</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-27.24</v>
+        <v>29.61</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>24科学城MTN002(项目收益)</t>
+          <t>26苏元禾MTN001B(科创债)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.01Y+4.00Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7045</t>
+          <t>1.8007</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7000</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>北京未来科学城发展集团有限公司</t>
+          <t>苏州元禾控股股份有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 18.56</t>
+          <t>C+ 31.52</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3299,7 +3297,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3313,9 +3311,11 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.6333</v>
-      </c>
-      <c r="V14" s="3"/>
+        <v>3.26</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3334,17 +3334,17 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>北京市-昌平区</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本次债券的募集资金扣除发行费用后,拟用于偿还到期中期票据(项目收益)[21科学城MTN003B(项目收益)]</t>
+          <t>本期债务融资工具发行拟募集资金10亿元,其中5亿元用于置换发行人一年以内用于科技创新领域股权投资或基金出资的自有资金投入,5亿元用于归还发行人到期债券[21元禾债01]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>北京未来科学城发展集团有限公司2026年度第六期中期票据(项目收益)</t>
+          <t>苏州元禾控股股份有限公司2026年度第二期科技创新债券(品种二)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2041-09-03</t>
+          <t>2031-09-03</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3396,37 +3396,33 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP14" s="3"/>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AV14" s="3" t="inlineStr">
@@ -3436,7 +3432,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3454,22 +3450,22 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26苏元禾MTN002B(科创债)</t>
+          <t>26常投K1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683476.IB</t>
+          <t>245963.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -3480,48 +3476,48 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.61 ~ 1.91</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>29.61</v>
+        <v>39.72</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26苏元禾MTN001B(科创债)</t>
+          <t>25常州投资MTN001</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>3.35Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.8007</t>
+          <t>1.7801</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>1.7800/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>苏州元禾控股股份有限公司</t>
+          <t>常州投资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.52</t>
+          <t>C+ 33.59</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3531,7 +3527,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3545,19 +3541,17 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>5.18</v>
+      </c>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3568,23 +3562,23 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金10亿元,其中5亿元用于置换发行人一年以内用于科技创新领域股权投资或基金出资的自有资金投入,5亿元用于归还发行人到期债券[21元禾债01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不低于70%部分出资用于支持科技创新领域发展相关的基金或置换相关基金出资,剩余部分用于偿还有息负债等符合监管要求的用途。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,渤海银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,东海证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3594,12 +3588,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>苏州元禾控股股份有限公司2026年度第二期科技创新债券(品种二)</t>
+          <t>常州投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3609,18 +3603,18 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-03</t>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
@@ -3630,28 +3624,32 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP15" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>通用机械</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3684,7 +3682,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26常投K1</t>
+          <t>26益阳01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3694,7 +3692,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>245963.SH</t>
+          <t>520452.SZ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3710,48 +3708,48 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>39.72</v>
+        <v>57.72</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>25常州投资MTN001</t>
+          <t>19益阳01</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>3.35Y</t>
+          <t>114D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7801</t>
+          <t>1.5990</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.7800/--</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>常州投资集团有限公司</t>
+          <t>益阳市城市建设投资运营集团有限责任公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.59</t>
+          <t>C- 19.02</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3761,7 +3759,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3775,41 +3773,45 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>5.18</v>
+        <v>4.18</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.05%~2.15%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>湖南省-益阳市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不低于70%部分出资用于支持科技创新领域发展相关的基金或置换相关基金出资,剩余部分用于偿还有息负债等符合监管要求的用途。</t>
+          <t>本期公司债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金或置换偿还公司债券本金的自有资金[23益阳01]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,东海证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>益阳市发展投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3822,17 +3824,17 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>常州投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>益阳市城市建设投资运营集团有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
@@ -3848,7 +3850,7 @@
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
@@ -3858,12 +3860,12 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -3873,17 +3875,17 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>通用机械</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3893,7 +3895,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3916,74 +3918,66 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26益阳01</t>
+          <t>26国金集团MTN001(并购)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>520452.SZ</t>
+          <t>102683516.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.45 ~ 1.85</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>57.72</v>
+        <v>9.61</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>19益阳01</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>114D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.5990</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.6100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>益阳市城市建设投资运营集团有限责任公司</t>
+          <t>江苏省国金投资集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 19.02</t>
+          <t>C+ 35.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3993,7 +3987,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4007,48 +4001,42 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="V17" s="3"/>
+        <v>2.13</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.05%~2.15%</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
+      <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>湖南省-益阳市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金或置换偿还公司债券本金的自有资金[23益阳01]</t>
+          <t>本期并购票据发行规模为20亿元,全部用于偿还发行人金融机构借款(并购贷款)</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>益阳市发展投资集团有限公司</t>
-        </is>
-      </c>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4058,33 +4046,33 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>益阳市城市建设投资运营集团有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江苏省国金投资集团有限公司2026年度第一期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t>2031-09-03</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4094,47 +4082,43 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP17" s="3"/>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4152,119 +4136,131 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26国金集团MTN001(并购)</t>
+          <t>26苏州高新MTN008</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683516.IB</t>
+          <t>102683522.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 1.85</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>9.61</v>
+        <v>34.47</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>24苏州高新MTN007B</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>2.93Y</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>1.7448</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>1.7600/1.7000</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>苏州苏高新集团有限公司</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>C- 23.69</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>09-02 09:00</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>江苏省国金投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>C+ 35.00</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>09-02 09:00</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.13</v>
+        <v>8.1</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.0</v>
+        <v>1.375</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
-        </is>
-      </c>
-      <c r="Y18" s="3"/>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期并购票据发行规模为20亿元,全部用于偿还发行人金融机构借款(并购贷款)</t>
+          <t>发行人本次发行金额3亿元债务融资工具,全部用于偿还到期有息债务[23苏州高新MTN004]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4285,7 +4281,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>江苏省国金投资集团有限公司2026年度第一期中期票据(并购)</t>
+          <t>苏州苏高新集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4295,74 +4291,78 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-03</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY18" s="3" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP18" s="3"/>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-03</t>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ18" s="3"/>
@@ -4370,74 +4370,66 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26苏州高新MTN008</t>
+          <t>26国金集团SCP001</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683522.IB</t>
+          <t>012682197.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>34.47</v>
+        <v>12.12</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>24苏州高新MTN007B</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>2.93Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7448</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>苏州苏高新集团有限公司</t>
+          <t>江苏省国金投资集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 23.69</t>
+          <t>C+ 35.00</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4457,50 +4449,46 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.375</v>
+        <v>1.0</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
-        </is>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>1.58%~1.62%</t>
+        </is>
+      </c>
+      <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行金额3亿元债务融资工具,全部用于偿还到期有息债务[23苏州高新MTN004]</t>
+          <t>本次募集资金50,000.00万元用于偿还银行贷款7,804.20万元、购买固定资产及装修36,895.80万元、购买软硬件设施5,300.00万元</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4515,7 +4503,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>苏州苏高新集团有限公司2026年度第八期中期票据</t>
+          <t>江苏省国金投资集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4525,13 +4513,13 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4541,37 +4529,33 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP19" s="3"/>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4596,7 +4580,7 @@
       </c>
       <c r="AY19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ19" s="3"/>
@@ -4604,7 +4588,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26国金集团SCP001</t>
+          <t>26中交租赁SCP005</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4614,7 +4598,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>012682197.IB</t>
+          <t>012682196.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4623,10 +4607,10 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -4634,89 +4618,101 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.12</v>
+        <v>17.12</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>24交租V1</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>278D</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>1.5683</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>1.6000/--</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>中交融资租赁有限公司</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>C- 13.09</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>09-02 09:00</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>江苏省国金投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t>C+ 35.00</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>09-02 09:00</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.4</v>
+        <v>3.3833</v>
       </c>
       <c r="V20" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.62%</t>
-        </is>
-      </c>
-      <c r="Y20" s="3"/>
+          <t>1.53%~1.57%</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金50,000.00万元用于偿还银行贷款7,804.20万元、购买固定资产及装修36,895.80万元、购买软硬件设施5,300.00万元</t>
+          <t>本期超短期融资券拟募集资金6亿元,拟全部用于偿还发行人即将到期的债务融资工具[26中交租赁SCP003]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司</t>
+          <t>上海银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4727,7 +4723,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4737,7 +4733,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>江苏省国金投资集团有限公司2026年度第一期超短期融资券</t>
+          <t>中交融资租赁有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4771,7 +4767,11 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP20" s="3"/>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -4779,17 +4779,17 @@
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26中交租赁SCP005</t>
+          <t>26南海农商行绿债01B</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4832,64 +4832,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>012682196.IB</t>
+          <t>222680020.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>17.12</v>
+        <v>48.72</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>24交租V1</t>
+          <t>25南海农商行债01</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>278D</t>
+          <t>2.18Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.5683</t>
+          <t>1.6179</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>1.6300/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>中交融资租赁有限公司</t>
+          <t>广东南海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 13.09</t>
+          <t>B+ 57.87</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4909,23 +4909,19 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>3.3833</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.57%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4933,31 +4929,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z21" s="3"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金6亿元,拟全部用于偿还发行人即将到期的债务融资工具[26中交租赁SCP003]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>中交融资租赁有限公司2026年度第五期超短期融资券</t>
+          <t>广东南海农村商业银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4977,25 +4977,25 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>金融</t>
@@ -5008,22 +5008,22 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5056,17 +5056,17 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26南海农商行绿债01B</t>
+          <t>26泉州文旅MTN003</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>222680020.IB</t>
+          <t>102683478.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.0</v>
+        <v>2.5</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -5086,44 +5086,44 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>48.72</v>
+        <v>44.47</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>25南海农商行债01</t>
+          <t>24泉旅04</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6179</t>
+          <t>1.6876</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>1.6300/--</t>
+          <t>1.7800/1.7000</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>广东南海农村商业银行股份有限公司</t>
+          <t>泉州文化旅游发展集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.87</t>
+          <t>C 28.65</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5146,52 +5146,52 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.71</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
+          <t>发行人本期中期票据发行金额5亿元,拟全部用于偿还发行人存量债务融资工具本金[23泉州文旅MTN003]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>广东南海农村商业银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
+          <t>泉州文化旅游发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
@@ -5232,32 +5232,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="AY22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AZ22" s="3"/>
@@ -5290,7 +5290,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26泉州文旅MTN003</t>
+          <t>26泉州文旅MTN003B(取消发行)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5300,54 +5300,48 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683478.IB</t>
+          <t>DY102683479.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>44.47</v>
-      </c>
+          <t>1.60 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>24泉旅04</t>
+          <t>26泉州文旅MTN001</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>4.60Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6876</t>
+          <t>1.8302</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5380,12 +5374,8 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U23" s="4" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.71</v>
-      </c>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -5393,7 +5383,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5435,7 +5425,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>泉州文化旅游发展集团有限公司2026年度第三期中期票据</t>
+          <t>泉州文化旅游发展集团有限公司2026年度第三期中期票据(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5445,7 +5435,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5524,53 +5514,59 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26泉州文旅MTN003B(取消发行)</t>
+          <t>26曹国07</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>DY102683479.IB</t>
+          <t>245951.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>5.5</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>62.72</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26泉州文旅MTN001</t>
+          <t>24曹妃国控MTN004</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.60Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.8302</t>
+          <t>1.9241</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5580,12 +5576,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>泉州文化旅游发展集团有限公司</t>
+          <t>曹妃甸国控投资集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C 28.65</t>
+          <t>C+ 32.43</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5595,7 +5591,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5608,43 +5604,49 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="4" t="n">
+        <v>3.87</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z24" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额5亿元,拟全部用于偿还发行人存量债务融资工具本金[23泉州文旅MTN003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5654,12 +5656,12 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>泉州文化旅游发展集团有限公司2026年度第三期中期票据(品种二)(取消发行)</t>
+          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5669,18 +5671,18 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
@@ -5690,27 +5692,27 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
@@ -5740,7 +5742,7 @@
       </c>
       <c r="AY24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ24" s="3"/>
@@ -5748,7 +5750,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26曹国07</t>
+          <t>26海创Y1</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5758,49 +5760,49 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>245951.SH</t>
+          <t>283897.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.5</v>
+        <v>6.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>62.72</v>
+        <v>56.72</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>24曹妃国控MTN004</t>
+          <t>26海创02</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>2.60Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.9241</t>
+          <t>1.7200</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5810,12 +5812,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司</t>
+          <t>宁波海创集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.43</t>
+          <t>D- 0.86</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5839,17 +5841,17 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.87</v>
+        <v>3.18</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5857,24 +5859,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金。[23海创02]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
+          <t>甬兴证券有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5895,12 +5893,12 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
+          <t>宁波海创集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
@@ -5916,7 +5914,7 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
@@ -5931,7 +5929,7 @@
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -5941,12 +5939,12 @@
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
@@ -5966,12 +5964,12 @@
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY25" s="3" t="inlineStr">
@@ -5984,7 +5982,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26海创Y1</t>
+          <t>26扬州03</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5994,12 +5992,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>283897.SH</t>
+          <t>283768.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -6010,33 +6008,33 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>56.72</v>
+        <v>57.61</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26海创02</t>
+          <t>26扬州02</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.60Y</t>
+          <t>4.64Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7200</t>
+          <t>1.9555</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -6046,12 +6044,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>宁波海创集团有限公司</t>
+          <t>扬州广合国有资本运营集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D- 0.86</t>
+          <t>C- 15.80</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6061,7 +6059,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6075,38 +6073,38 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金。[23海创02]</t>
+          <t>本期债券发行规模为人民币6.00亿元整,本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金。[23扬州04]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>甬兴证券有限公司,华福证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6127,7 +6125,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>宁波海创集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+          <t>扬州广合国有资本运营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6137,7 +6135,7 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6158,7 +6156,7 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
@@ -6168,22 +6166,22 @@
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6198,12 +6196,12 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY26" s="3" t="inlineStr">
@@ -6216,7 +6214,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26扬州03</t>
+          <t>26三能K1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6226,64 +6224,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>283768.SH</t>
+          <t>245905.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>57.61</v>
+        <v>34.39</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26扬州02</t>
+          <t>24三峡新能MTN002</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.64Y</t>
+          <t>7.76Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.9555</t>
+          <t>1.9466</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9700/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>扬州广合国有资本运营集团有限公司</t>
+          <t>中国三峡新能源(集团)股份有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 15.80</t>
+          <t>C- 16.92</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6307,38 +6305,42 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.25</v>
+        <v>4.22</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z27" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为人民币6.00亿元整,本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金。[23扬州04]</t>
+          <t>本期债券的募集资金扣除发行费用后拟全部用于生产性支出,包括偿还公司有息债务、补充流动资金、项目建设及运营等符合法律法规规定的用途。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6349,7 +6351,7 @@
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
@@ -6359,17 +6361,17 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>扬州广合国有资本运营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>中国三峡新能源(集团)股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2036-09-04</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6390,32 +6392,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6448,7 +6450,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26三能K1</t>
+          <t>26菏财GT01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6458,64 +6460,64 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>245905.SH</t>
+          <t>520445.SZ</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
+        <v>2.5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>34.39</v>
+        <v>49.61</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24三峡新能MTN002</t>
+          <t>26菏财01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>7.76Y</t>
+          <t>2.65Y+2.00Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.9466</t>
+          <t>1.8637</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.9700/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中国三峡新能源(集团)股份有限公司</t>
+          <t>菏泽财金投资集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 16.92</t>
+          <t>B- 38.33</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6525,7 +6527,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6539,42 +6541,38 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>4.22</v>
+        <v>3.05</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省-菏泽市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后拟全部用于生产性支出,包括偿还公司有息债务、补充流动资金、项目建设及运营等符合法律法规规定的用途。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,平安证券股份有限公司</t>
+          <t>国投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6585,27 +6583,27 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中国三峡新能源(集团)股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>菏泽财金投资集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2036-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6616,7 +6614,7 @@
       </c>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
@@ -6626,37 +6624,37 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6666,7 +6664,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6684,7 +6682,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26菏财GT01</t>
+          <t>26珠华04</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6694,64 +6692,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>520445.SZ</t>
+          <t>520444.SZ</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>2+2+1</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>49.61</v>
+        <v>134.61</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26菏财01</t>
+          <t>25珠华02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.65Y+2.00Y</t>
+          <t>2.21Y+2.00Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.8637</t>
+          <t>2.8118</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>菏泽财金投资集团有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>B- 38.33</t>
+          <t>B- 38.58</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6775,38 +6773,38 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>2.73%~2.83%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>山东省-菏泽市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于置换到期的公司债券本金[23珠华Y3]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>华金证券股份有限公司,国泰海通证券股份有限公司,西部证券股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,国信证券股份有限公司,中国银河证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6827,7 +6825,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>菏泽财金投资集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)(品种一)</t>
+          <t>珠海华发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6848,7 +6846,7 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6858,37 +6856,37 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6916,7 +6914,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26珠华04</t>
+          <t>26淮开06</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6926,64 +6924,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>520444.SZ</t>
+          <t>283873.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2+2+1</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>4.3</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.0</v>
+        <v>4.3</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.75</v>
+        <v>1.72</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>134.61</v>
+        <v>40.47</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25珠华02</t>
+          <t>26淮开04</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.21Y+2.00Y</t>
+          <t>1.96Y+3.00Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2.8118</t>
+          <t>1.7086</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>淮安开发控股有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 38.58</t>
+          <t>C- 23.78</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7007,38 +7005,38 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.3</v>
+        <v>3.95</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>2.73%~2.83%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于置换到期的公司债券本金[23珠华Y3]</t>
+          <t>本期债券的募集资金扣除发行费用后拟用于偿还发行人公司债券本金[23淮开05]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司,国泰海通证券股份有限公司,西部证券股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,国信证券股份有限公司,中国银河证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>国信证券股份有限公司,国金证券股份有限公司,中国银河证券股份有限公司,中邮证券有限责任公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7054,12 +7052,12 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>淮安开发控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7069,7 +7067,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2030-09-04</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7090,32 +7088,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7148,7 +7146,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26淮开06</t>
+          <t>26怀科01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7158,64 +7156,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283873.SH</t>
+          <t>283753.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.3</v>
+        <v>3.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.3</v>
+        <v>3.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>40.47</v>
+        <v>37.61</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26淮开04</t>
+          <t>26怀柔科学PPN002</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1.96Y+3.00Y</t>
+          <t>2.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7086</t>
+          <t>1.7591</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>淮安开发控股有限公司</t>
+          <t>北京怀柔科学城建设发展有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 23.78</t>
+          <t>C- 23.93</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7225,7 +7223,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7239,38 +7237,42 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.95</v>
+        <v>3.13</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z31" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>北京市-怀柔区</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后拟用于偿还发行人公司债券本金[23淮开05]</t>
+          <t>本期公司债券募集资金拟用于偿还到期的公司债券[23怀科01]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,国金证券股份有限公司,中国银河证券股份有限公司,中邮证券有限责任公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7291,7 +7293,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>淮安开发控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7301,7 +7303,7 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2030-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
@@ -7322,12 +7324,12 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
@@ -7337,12 +7339,12 @@
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
@@ -7352,7 +7354,7 @@
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7380,7 +7382,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26怀科01</t>
+          <t>26怀科02</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7390,12 +7392,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>283753.SH</t>
+          <t>283754.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7406,38 +7408,38 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>37.61</v>
+        <v>41.95</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26怀柔科学PPN002</t>
+          <t>24怀科03</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+2.00Y</t>
+          <t>3.18Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7591</t>
+          <t>1.7890</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7700</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -7471,7 +7473,7 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.13</v>
+        <v>2.27</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
@@ -7481,7 +7483,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7501,7 +7503,7 @@
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于偿还到期的公司债券[23怀科01]</t>
+          <t>本期公司债券募集资金拟用于偿还到期的公司债券。[23怀科01]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
@@ -7527,7 +7529,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7537,58 +7539,62 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
+          <t>2033-09-04</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t>2031-09-04</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
-      <c r="AL32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV32" s="3" t="inlineStr">
@@ -7616,7 +7622,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26怀科02</t>
+          <t>26沂投03</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7626,64 +7632,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>283754.SH</t>
+          <t>283864.SH</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.0</v>
+        <v>5.9</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.0</v>
+        <v>5.9</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>41.95</v>
+        <v>57.72</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24怀科03</t>
+          <t>26沂投02</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>3.18Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7890</t>
+          <t>1.8701</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/1.7700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司</t>
+          <t>新沂市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 23.93</t>
+          <t>C 29.69</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7693,7 +7699,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7703,49 +7709,49 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.27</v>
+        <v>4.1525</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>北京市-怀柔区</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于偿还到期的公司债券。[23怀科01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23沂投05]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3"/>
+          <t>国金证券股份有限公司,天风证券股份有限公司,国投证券股份有限公司,南京证券股份有限公司,兴业证券股份有限公司,东兴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>江苏钟吾城乡投资发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7763,7 +7769,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>新沂市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7773,72 +7779,68 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2033-09-04</t>
-        </is>
-      </c>
-      <c r="AK33" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-03</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-04</t>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7856,74 +7858,74 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26菏财GT02</t>
+          <t>26厦门银行债01</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>520446.SZ</t>
+          <t>212680031.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.5</v>
+        <v>30.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>80.61</v>
+        <v>33.72</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25菏财04</t>
+          <t>25厦门银行科创债01(柜台)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.25Y</t>
+          <t>4.03Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.1338</t>
+          <t>1.6337</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>2.1300/2.1300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>菏泽财金投资集团有限公司</t>
+          <t>厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 38.33</t>
+          <t>B 51.58</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7933,7 +7935,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7946,81 +7948,79 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U34" s="4" t="n">
-        <v>3.33</v>
-      </c>
+      <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>山东省-菏泽市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
+          <t>用于优化发行人负债结构，充实营运资金，促进业务稳健发展，优先用于支持科技创新领域信贷投放，其中重点支持专精特新企业，加大对科技创新的支持力度。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,国开证券股份有限公司,中国银行股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,交通银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>菏泽财金投资集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)(品种二)</t>
+          <t>厦门银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN34" s="3" t="inlineStr">
@@ -8030,32 +8030,32 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8088,72 +8088,74 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26深投08</t>
+          <t>26酒钢MTN003</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>524988.SZ</t>
+          <t>102683525.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F35" s="3"/>
+      <c r="F35" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.70 ~ 2.20</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>39.39</v>
+        <v>61.41</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26深投控MTN004B</t>
+          <t>25酒钢MTN001(科创债)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>9.89Y</t>
+          <t>2.06Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2.1167</t>
+          <t>1.8257</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>2.1300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司</t>
+          <t>酒泉钢铁(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 22.15</t>
+          <t>C- 13.33</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8163,7 +8165,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8173,19 +8175,23 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>3.25</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8193,30 +8199,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>甘肃省-嘉峪关市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
+          <t>本期永续中期票据发行拟募集资金5亿元,所募集资金拟用于归还金融机构贷款及支付氧化铝货款。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -8226,12 +8228,12 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
+          <t>酒泉钢铁(集团)有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8241,64 +8243,60 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2036-09-07</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-09-04</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>普钢</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO35" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ35" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR35" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8306,40 +8304,42 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AZ35" s="3"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AZ35" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26嘉善国控MTN005</t>
+          <t>26南海农商行绿债01A</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683521.IB</t>
+          <t>222680019.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -8350,48 +8350,48 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>34.61</v>
+        <v>37.72</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26嘉善国控MTN004</t>
+          <t>25南海农商行债01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>4.88Y</t>
+          <t>2.18Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.8436</t>
+          <t>1.6179</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.8350/1.8300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>嘉善县国创资本控股集团有限公司</t>
+          <t>广东南海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 38.79</t>
+          <t>B+ 57.87</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8414,12 +8414,8 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U36" s="4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>1.43</v>
-      </c>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -8427,7 +8423,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8435,31 +8431,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行规模7亿元,募集资金用于偿还发行人下属子公司存量债务融资工具本金。[23嘉善国投PPN004]</t>
+          <t>发行人本次拟发行规模不超过8亿元人民币的绿色金融债券,募集资金拟投向符合《绿色金融支持项目目录(2025年版)》标准的绿色储备项目共9项,项目拟使用绿色债券募集资金8.40亿元人民币。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,杭州银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>嘉善县国创资本控股集团有限公司2026年度第五期中期票据</t>
+          <t>广东南海农村商业银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
@@ -8500,32 +8500,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="AY36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ36" s="3"/>
@@ -8558,74 +8558,74 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26渤海银行债01</t>
+          <t>26菏财GT02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-02 17:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>212680029.IB</t>
+          <t>520446.SZ</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>100.0</v>
+        <v>2.5</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>150.0</v>
+        <v>3.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.6</v>
+        <v>2.21</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>34.72</v>
+        <v>80.61</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25渤海银行债02A</t>
+          <t>25菏财04</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>4.25Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6002</t>
+          <t>2.1338</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.6100/--</t>
+          <t>2.1300/2.1300</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>菏泽财金投资集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>A- 60.94</t>
+          <t>B- 38.33</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8648,47 +8648,45 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U37" s="3"/>
+      <c r="U37" s="4" t="n">
+        <v>3.33</v>
+      </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>2.21%~2.31%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省-菏泽市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源 ，优化负债期限结构 ，促进业务的稳健发展 。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,华夏银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,国投证券股份有限公司,国开证券股份有限公司,东方证券股份有限公司</t>
+          <t>国投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8698,28 +8696,28 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司2026年金融债券(第一期)</t>
+          <t>菏泽财金投资集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
@@ -8734,32 +8732,32 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8792,7 +8790,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26沂投03</t>
+          <t>26深投08</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8802,64 +8800,62 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>283864.SH</t>
+          <t>524988.SZ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>5.9</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>57.72</v>
+        <v>39.39</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26沂投02</t>
+          <t>26深投控MTN004B</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>9.89Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.8701</t>
+          <t>2.1167</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.8900/1.8700</t>
+          <t>2.1300/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>新沂市城市投资发展集团有限公司</t>
+          <t>深圳市投资控股有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C 29.69</t>
+          <t>C- 22.15</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8879,49 +8875,47 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="n">
-        <v>4.1525</v>
-      </c>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z38" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23沂投05]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,天风证券股份有限公司,国投证券股份有限公司,南京证券股份有限公司,兴业证券股份有限公司,东兴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3" t="inlineStr">
-        <is>
-          <t>江苏钟吾城乡投资发展集团有限公司</t>
-        </is>
-      </c>
+          <t>国信证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8934,48 +8928,52 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>新沂市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2036-09-07</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
@@ -8985,17 +8983,17 @@
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9005,7 +9003,7 @@
       </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -9028,74 +9026,74 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26蓉产02</t>
+          <t>26嘉善国控MTN005</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>524985.SZ</t>
+          <t>102683521.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-0.61</v>
+        <v>34.61</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26成都产投MTN003</t>
+          <t>26嘉善国控MTN004</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.92Y+5.00Y</t>
+          <t>4.88Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.8002</t>
+          <t>1.8436</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8350/1.8300</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>成都产业投资集团有限公司</t>
+          <t>嘉善县国创资本控股集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.16</t>
+          <t>B- 38.79</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9105,7 +9103,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9119,17 +9117,19 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>5.3</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.43</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9140,23 +9140,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券拟募集资金不超过10.00亿元(含10.00亿元),扣除发行费用后,拟用于生产性支出,具体包括偿还到期债务以及相关适用法律法规及/或监管机构允许的用途,具体用途根据公司资金需求情况确定。</t>
+          <t>发行人本期中期票据发行规模7亿元,募集资金用于偿还发行人下属子公司存量债务融资工具本金。[23嘉善国投PPN004]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>宁波银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>成都产业投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>嘉善县国创资本控股集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9181,60 +9181,60 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2036-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AO39" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ39" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR39" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-04</t>
-        </is>
-      </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="AY39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AZ39" s="3"/>
@@ -9260,7 +9260,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26曹国08</t>
+          <t>26蓉产02</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9270,64 +9270,64 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>245952.SH</t>
+          <t>524985.SZ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4.5</v>
+        <v>10.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>66.61</v>
+        <v>-0.61</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26曹妃国控MTN003B</t>
+          <t>26成都产投MTN003</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.62Y</t>
+          <t>4.92Y+5.00Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2.1430</t>
+          <t>1.8002</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>2.1400/2.1200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司</t>
+          <t>成都产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.43</t>
+          <t>C+ 30.16</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9351,17 +9351,17 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.98</v>
+        <v>6.38</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9369,24 +9369,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z40" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
+          <t>本期公司债券拟募集资金不超过10.00亿元(含10.00亿元),扣除发行费用后,拟用于生产性支出,具体包括偿还到期债务以及相关适用法律法规及/或监管机构允许的用途,具体用途根据公司资金需求情况确定。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
+          <t>国金证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
@@ -9402,12 +9398,12 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
+          <t>成都产业投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9417,7 +9413,7 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2036-09-04</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
@@ -9428,7 +9424,7 @@
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN40" s="3" t="inlineStr">
@@ -9443,7 +9439,7 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
@@ -9453,12 +9449,12 @@
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
@@ -9468,7 +9464,7 @@
       </c>
       <c r="AU40" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AV40" s="3" t="inlineStr">
@@ -9478,7 +9474,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9496,7 +9492,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>赣投YK08</t>
+          <t>26曹国08</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9506,64 +9502,64 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>245982.SH</t>
+          <t>245952.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>15.0</v>
+        <v>4.5</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>37.72</v>
+        <v>66.61</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>赣投YK04</t>
+          <t>26曹妃国控MTN003B</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.86Y+N</t>
+          <t>4.62Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.6882</t>
+          <t>2.1430</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.6950</t>
+          <t>2.1400/2.1200</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>江西省投资集团有限公司</t>
+          <t>曹妃甸国控投资集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 38.24</t>
+          <t>C+ 32.43</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9573,7 +9569,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9587,17 +9583,17 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2.61</v>
+        <v>3.98</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9605,20 +9601,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z41" s="3"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江西省</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过15.00亿元,扣除相关发行费用后拟将不超过10.00亿元偿还到期公司债券本金;不超过5.00亿元偿还有息债务。[赣投YK01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司,广发证券股份有限公司</t>
+          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>江西省投资集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第三期)</t>
+          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>燃气</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9728,40 +9728,40 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26酒钢MTN003</t>
+          <t>赣投YK08</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>102683525.IB</t>
+          <t>245982.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>61.41</v>
+        <v>37.72</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -9770,32 +9770,32 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25酒钢MTN001(科创债)</t>
+          <t>赣投YK04</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.06Y</t>
+          <t>2.86Y+N</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.8257</t>
+          <t>1.6882</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/1.6950</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>酒泉钢铁(集团)有限责任公司</t>
+          <t>江西省投资集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 13.33</t>
+          <t>B- 38.24</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9819,19 +9819,17 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>3.25</v>
-      </c>
+        <v>2.61</v>
+      </c>
+      <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -9842,23 +9840,23 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>甘肃省-嘉峪关市</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期永续中期票据发行拟募集资金5亿元,所募集资金拟用于归还金融机构贷款及支付氧化铝货款。</t>
+          <t>本期债券发行规模为不超过15.00亿元,扣除相关发行费用后拟将不超过10.00亿元偿还到期公司债券本金;不超过5.00亿元偿还有息债务。[赣投YK01]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,东兴证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9868,12 +9866,12 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>酒泉钢铁(集团)有限责任公司2026年度第三期中期票据</t>
+          <t>江西省投资集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9883,18 +9881,18 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
@@ -9909,27 +9907,27 @@
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>燃气</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9949,17 +9947,15 @@
       </c>
       <c r="AX42" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AZ42" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AZ42" s="3"/>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
@@ -13234,74 +13230,74 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26厦门银行债01</t>
+          <t>26临平交通PPN004</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>212680031.IB</t>
+          <t>032680513.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>33.72</v>
+        <v>34.61</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>25厦门银行科创债01(柜台)</t>
+          <t>26临交01</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>4.03Y</t>
+          <t>2.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.6337</t>
+          <t>1.7538</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>厦门银行股份有限公司</t>
+          <t>杭州临平交通集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>B 51.58</t>
+          <t>B- 35.14</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13324,8 +13320,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
+      <c r="U57" s="4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V57" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
           <t>5+</t>
@@ -13333,39 +13333,39 @@
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>用于优化发行人负债结构，充实营运资金，促进业务稳健发展，优先用于支持科技创新领域信贷投放，其中重点支持专精特新企业，加大对科技创新的支持力度。</t>
+          <t>本期发行金额人民币10亿元,拟用于偿还发行人本部有息债务[23临平交通PPN003]</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,国开证券股份有限公司,中国银行股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,交通银行股份有限公司,申万宏源证券有限公司</t>
+          <t>宁波银行股份有限公司,兴业银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG57" s="3" t="inlineStr">
@@ -13375,17 +13375,17 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>厦门银行股份有限公司2026年第一期金融债券</t>
+          <t>杭州临平交通集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="AM57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN57" s="3" t="inlineStr">
@@ -13406,37 +13406,37 @@
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX57" s="3" t="inlineStr">
@@ -13464,22 +13464,22 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26临平交通PPN004</t>
+          <t>26远东租赁MTN008</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>032680513.IB</t>
+          <t>102683520.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -13490,48 +13490,48 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.71 ~ 1.91</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>34.61</v>
+        <v>67.41</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26临交01</t>
+          <t>25远东六</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+2.00Y</t>
+          <t>1.98Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.7538</t>
+          <t>1.9400</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/1.8800</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>杭州临平交通集团有限公司</t>
+          <t>远东国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>B- 35.14</t>
+          <t>C- 21.30</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13555,46 +13555,44 @@
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>1.25</v>
-      </c>
+        <v>0.58</v>
+      </c>
+      <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额人民币10亿元,拟用于偿还发行人本部有息债务[23临平交通PPN003]</t>
+          <t>本期债务融资工具拟募集资金10.00亿元，5.00亿元用于偿还发行人即将到期的债务融资工具，5.00亿元用于偿还发行人及子公司金融机构借款[24远东租赁MTN006]</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,兴业银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
@@ -13609,17 +13607,17 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>杭州临平交通集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>远东国际融资租赁有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13630,7 +13628,7 @@
       </c>
       <c r="AM58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN58" s="3" t="inlineStr">
@@ -13640,37 +13638,37 @@
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV58" s="3" t="inlineStr">
@@ -13680,7 +13678,7 @@
       </c>
       <c r="AW58" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX58" s="3" t="inlineStr">
@@ -13690,15 +13688,17 @@
       </c>
       <c r="AY58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AZ58" s="3"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AZ58" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26远东租赁MTN008</t>
+          <t>26广西路建MTN002</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13708,64 +13708,64 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>102683520.IB</t>
+          <t>102683524.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.71 ~ 1.91</t>
+          <t>1.75 ~ 2.10</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>67.41</v>
+        <v>45.61</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>25远东六</t>
+          <t>25广西路建MTN002(科创债)</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>1.98Y</t>
+          <t>4.18Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.9400</t>
+          <t>2.0250</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/1.8800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>远东国际融资租赁有限公司</t>
+          <t>广西路建工程集团有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 21.30</t>
+          <t>D+ 5.45</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13789,38 +13789,40 @@
         </is>
       </c>
       <c r="U59" s="4" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="V59" s="3"/>
+        <v>2.6667</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>2.01%~2.11%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具拟募集资金10.00亿元，5.00亿元用于偿还发行人即将到期的债务融资工具，5.00亿元用于偿还发行人及子公司金融机构借款[24远东租赁MTN006]</t>
+          <t>本期中期票据募集资金3亿元,全部用于偿还到期银行借款</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,天津银行股份有限公司</t>
+          <t>中信银行股份有限公司,广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
@@ -13841,7 +13843,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>远东国际融资租赁有限公司2026年度第八期中期票据</t>
+          <t>广西路建工程集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13851,7 +13853,7 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
@@ -13862,7 +13864,7 @@
       </c>
       <c r="AM59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN59" s="3" t="inlineStr">
@@ -13872,32 +13874,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13925,14 +13927,12 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ59" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ59" s="3"/>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26广西路建MTN002</t>
+          <t>26海螺科创MTN001</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>102683524.IB</t>
+          <t>102683526.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -13951,55 +13951,55 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.75 ~ 2.10</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>45.61</v>
+        <v>22.61</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>25广西路建MTN002(科创债)</t>
+          <t>26康达新材MTN001(科创债)</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>4.18Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2.0250</t>
+          <t>2.9310</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.8300</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>广西路建工程集团有限公司</t>
+          <t>安徽海螺科创材料有限责任公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.45</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 10:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -14023,19 +14023,19 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>2.6667</v>
+        <v>4.98</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>5.0</v>
+        <v>2.08</v>
       </c>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>2.01%~2.11%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -14043,23 +14043,31 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z60" s="3"/>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金3亿元,全部用于偿还到期银行借款</t>
+          <t>发行人本次中期票据计划注册30亿元，其中15亿元用于偿还发行人及合并报表范围内子公司有息负债，15亿元用于补流。首期发行10亿元，其中7.4亿元用于偿还发行人及合并报表范围内子公司有息负债，2.6亿元用于补流</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,广西北部湾银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD60" s="3"/>
+          <t>兴业银行股份有限公司,徽商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr">
+        <is>
+          <t>安徽海螺集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE60" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -14077,7 +14085,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>广西路建工程集团有限公司2026年度第二期中期票据</t>
+          <t>安徽海螺科创材料有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14111,29 +14119,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="AP60" s="3"/>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14143,7 +14147,7 @@
       </c>
       <c r="AV60" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW60" s="3" t="inlineStr">
@@ -14166,74 +14170,74 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26海螺科创MTN001</t>
+          <t>26国耀04</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>102683526.IB</t>
+          <t>245990.SH</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>22.61</v>
+        <v>53.11</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26康达新材MTN001(科创债)</t>
+          <t>25国耀融汇MTN002</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>2.04Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>2.9310</t>
+          <t>1.8676</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/2.8300</t>
+          <t>--/1.8200</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺科创材料有限责任公司</t>
+          <t>国耀融汇融资租赁有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 18.43</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14243,7 +14247,7 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>09-02 10:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -14257,69 +14261,59 @@
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="V61" s="4" t="n">
-        <v>2.08</v>
-      </c>
+        <v>3.01</v>
+      </c>
+      <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z61" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据计划注册30亿元，其中15亿元用于偿还发行人及合并报表范围内子公司有息负债，15亿元用于补流。首期发行10亿元，其中7.4亿元用于偿还发行人及合并报表范围内子公司有息负债，2.6亿元用于补流</t>
+          <t>本期债券募集资金不超过6.00亿元用于偿还有息债务,剩余部分用于补充公司融资租赁业务、保理业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出[24控租03]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,徽商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD61" s="3" t="inlineStr">
-        <is>
-          <t>安徽海螺集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG61" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺科创材料有限责任公司2026年度第一期中期票据</t>
+          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14329,18 +14323,18 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN61" s="3" t="inlineStr">
@@ -14350,28 +14344,32 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP61" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -14381,7 +14379,7 @@
       </c>
       <c r="AV61" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW61" s="3" t="inlineStr">
@@ -14396,7 +14394,7 @@
       </c>
       <c r="AY61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ61" s="3"/>
@@ -14404,7 +14402,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26国耀04</t>
+          <t>26建邺01</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14414,64 +14412,64 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>245990.SH</t>
+          <t>283862.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>53.11</v>
+        <v>49.72</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>25国耀融汇MTN002</t>
+          <t>26建邺K2</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.04Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.8676</t>
+          <t>1.6902</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/1.8200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>国耀融汇融资租赁有限公司</t>
+          <t>南京市建邺区高新科技投资集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C- 18.43</t>
+          <t>C- 12.86</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14495,38 +14493,38 @@
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>3.01</v>
+        <v>6.38</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过6.00亿元用于偿还有息债务,剩余部分用于补充公司融资租赁业务、保理业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出[24控租03]</t>
+          <t>本期债券募集资金40,000.00万元拟全部用于置换回售公司债券发行人支付的自有资金[GC建邺01]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司</t>
+          <t>华泰联合证券有限责任公司,南京证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
@@ -14537,7 +14535,7 @@
       </c>
       <c r="AF62" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG62" s="3" t="inlineStr">
@@ -14547,17 +14545,17 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>南京市建邺区高新科技投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK62" s="3"/>
@@ -14578,32 +14576,32 @@
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14636,74 +14634,74 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26建邺01</t>
+          <t>26京东PPN002</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>283862.SH</t>
+          <t>032680509.IB</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>4.0</v>
+        <v>40.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>4.0</v>
+        <v>40.0</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>49.72</v>
+        <v>19.5</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26建邺K2</t>
+          <t>26京东PPN001</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>76D</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.6902</t>
+          <t>1.5120</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>南京市建邺区高新科技投资集团有限公司</t>
+          <t>北京京东世纪贸易有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>C- 12.86</t>
+          <t>D+ 8.80</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14713,7 +14711,7 @@
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr">
@@ -14727,59 +14725,61 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="V63" s="3"/>
+        <v>3.7375</v>
+      </c>
+      <c r="V63" s="4" t="n">
+        <v>2.05</v>
+      </c>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.63%~1.67%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金40,000.00万元拟全部用于置换回售公司债券发行人支付的自有资金[GC建邺01]</t>
+          <t>本期定向工具基础发行规模为0亿元，发行金额上限40亿元，募集资金用于偿还公司有息借款、银行承兑汇票及补充公司流动资金</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,南京证券股份有限公司</t>
+          <t>中国农业银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF63" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG63" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>南京市建邺区高新科技投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>北京京东世纪贸易有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14789,13 +14789,13 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
       <c r="AL63" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM63" s="3" t="inlineStr">
@@ -14810,32 +14810,32 @@
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>线上零售</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>线上零售</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
@@ -14868,74 +14868,74 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26京东PPN002</t>
+          <t>26渤海银行债01</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-02 17:00</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>032680509.IB</t>
+          <t>212680029.IB</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>40.0</v>
+        <v>100.0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>40.0</v>
+        <v>150.0</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>19.5</v>
+        <v>34.72</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26京东PPN001</t>
+          <t>25渤海银行债02A</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>76D</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.5120</t>
+          <t>1.6002</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>北京京东世纪贸易有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.80</t>
+          <t>A- 60.94</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14958,20 +14958,16 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U64" s="4" t="n">
-        <v>3.7375</v>
-      </c>
-      <c r="V64" s="4" t="n">
-        <v>2.05</v>
-      </c>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.67%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -14979,31 +14975,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z64" s="3"/>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期定向工具基础发行规模为0亿元，发行金额上限40亿元，募集资金用于偿还公司有息借款、银行承兑汇票及补充公司流动资金</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源 ，优化负债期限结构 ，促进业务的稳健发展 。</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,华夏银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,国投证券股份有限公司,国开证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
       <c r="AE64" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF64" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG64" s="3" t="inlineStr">
@@ -15013,17 +15013,17 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>北京京东世纪贸易有限公司2026年度第二期定向债务融资工具</t>
+          <t>渤海银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2027-06-01</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK64" s="3"/>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="AM64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN64" s="3" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
@@ -15054,22 +15054,22 @@
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>线上零售</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>线上零售</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-02.xlsx
+++ b/data/credit_bond_all_2026-09-02.xlsx
@@ -2298,29 +2298,29 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26九国04</t>
+          <t>26科学城MTN006(项目收益)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>283891.SH</t>
+          <t>102683532.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+3+3+3+3</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -2328,44 +2328,44 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>49.72</v>
+        <v>-27.24</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26九国03</t>
+          <t>24科学城MTN002(项目收益)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.89Y</t>
+          <t>3.01Y+4.00Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.7565</t>
+          <t>1.7045</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.7000</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>九江市国有投资控股集团有限公司</t>
+          <t>北京未来科学城发展集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 42.60</t>
+          <t>C- 19.36</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2385,11 +2385,11 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.16</v>
+        <v>4.6333</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2410,23 +2410,23 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江西省-九江市</t>
+          <t>北京市-昌平区</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券所募资金金额不超过10亿元（含10亿元），扣除发行费用后，用于偿还公司债券本金【23 九国V2】</t>
+          <t>本次债券的募集资金扣除发行费用后,拟用于偿还到期中期票据(项目收益)[21科学城MTN003B(项目收益)]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,华泰联合证券有限责任公司,光大证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2436,28 +2436,28 @@
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>九江市国有投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>北京未来科学城发展集团有限公司2026年度第六期中期票据(项目收益)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2041-09-03</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM10" s="3" t="inlineStr">
@@ -2467,30 +2467,42 @@
       </c>
       <c r="AN10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ10" s="3"/>
-      <c r="AR10" s="3"/>
-      <c r="AS10" s="3"/>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AV10" s="3" t="inlineStr">
@@ -2500,7 +2512,7 @@
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -2518,17 +2530,17 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26运河01</t>
+          <t>26苏元禾MTN002B(科创债)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>283877.SH</t>
+          <t>102683476.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2537,55 +2549,55 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.61 ~ 1.91</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>55.61</v>
+        <v>29.61</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>24古运河PPN001</t>
+          <t>26苏元禾MTN001B(科创债)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>1.22Y+2.00Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.7878</t>
+          <t>1.8007</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>江苏古运河投资集团有限公司</t>
+          <t>苏州元禾控股股份有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 29.35</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2595,7 +2607,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2605,52 +2617,50 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="V11" s="3"/>
+        <v>3.26</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券本金,或置换自有资金偿还的公司债券本金。[23运河01]</t>
+          <t>本期债务融资工具发行拟募集资金10亿元,其中5亿元用于置换发行人一年以内用于科技创新领域股权投资或基金出资的自有资金投入,5亿元用于归还发行人到期债券[21元禾债01]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>无锡市城南建设投资发展有限公司</t>
-        </is>
-      </c>
+          <t>中国建设银行股份有限公司,渤海银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2660,68 +2670,64 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>江苏古运河投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>苏州元禾控股股份有限公司2026年度第二期科技创新债券(品种二)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2031-09-03</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP11" s="3"/>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2731,7 +2737,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
@@ -2754,74 +2760,74 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26科学城MTN006(项目收益)</t>
+          <t>26常投K1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683532.IB</t>
+          <t>245963.SH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3+3+3+3+3</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-27.24</v>
+        <v>39.72</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>24科学城MTN002(项目收益)</t>
+          <t>25常州投资MTN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.01Y+4.00Y</t>
+          <t>3.35Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7045</t>
+          <t>1.7801</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7000</t>
+          <t>1.7800/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>北京未来科学城发展集团有限公司</t>
+          <t>常州投资集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 19.36</t>
+          <t>B- 38.08</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2831,7 +2837,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2845,17 +2851,17 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>4.6333</v>
+        <v>5.18</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2866,23 +2872,23 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>北京市-昌平区</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本次债券的募集资金扣除发行费用后,拟用于偿还到期中期票据(项目收益)[21科学城MTN003B(项目收益)]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不低于70%部分出资用于支持科技创新领域发展相关的基金或置换相关基金出资,剩余部分用于偿还有息负债等符合监管要求的用途。</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,东海证券股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2892,12 +2898,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>北京未来科学城发展集团有限公司2026年度第六期中期票据(项目收益)</t>
+          <t>常州投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2907,18 +2913,18 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2041-09-03</t>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
@@ -2928,37 +2934,37 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>通用机械</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AV12" s="3" t="inlineStr">
@@ -2968,7 +2974,7 @@
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2986,22 +2992,22 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26苏元禾MTN002B(科创债)</t>
+          <t>26益阳01</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683476.IB</t>
+          <t>520452.SZ</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -3012,48 +3018,48 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.61 ~ 1.91</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>29.61</v>
+        <v>57.72</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26苏元禾MTN001B(科创债)</t>
+          <t>19益阳01</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>114D</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.8007</t>
+          <t>1.5990</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>苏州元禾控股股份有限公司</t>
+          <t>益阳市城市建设投资运营集团有限责任公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 29.35</t>
+          <t>C- 14.57</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3063,7 +3069,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3077,46 +3083,48 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>4.18</v>
+      </c>
+      <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>2.05%~2.15%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>湖南省-益阳市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行拟募集资金10亿元,其中5亿元用于置换发行人一年以内用于科技创新领域股权投资或基金出资的自有资金投入,5亿元用于归还发行人到期债券[21元禾债01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金或置换偿还公司债券本金的自有资金[23益阳01]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD13" s="3"/>
+          <t>国金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>益阳市发展投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3126,28 +3134,28 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>苏州元禾控股股份有限公司2026年度第二期科技创新债券(品种二)</t>
+          <t>益阳市城市建设投资运营集团有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-03</t>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3162,28 +3170,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP13" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3193,7 +3205,7 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW13" s="3" t="inlineStr">
@@ -3216,74 +3228,66 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26常投K1</t>
+          <t>26国金集团MTN001(并购)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>245963.SH</t>
+          <t>102683516.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.45 ~ 1.85</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>39.72</v>
+        <v>9.61</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>25常州投资MTN001</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>3.35Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7801</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.7800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>常州投资集团有限公司</t>
+          <t>江苏省国金投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 38.08</t>
+          <t>C+ 35.00</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3293,7 +3297,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3307,44 +3311,42 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="V14" s="3"/>
+        <v>2.13</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
+      <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不低于70%部分出资用于支持科技创新领域发展相关的基金或置换相关基金出资,剩余部分用于偿还有息负债等符合监管要求的用途。</t>
+          <t>本期并购票据发行规模为20亿元,全部用于偿还发行人金融机构借款(并购贷款)</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,东海证券股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3354,12 +3356,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>常州投资集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>江苏省国金投资集团有限公司2026年度第一期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3369,18 +3371,18 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t>2031-09-03</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3390,37 +3392,33 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP14" s="3"/>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>通用机械</t>
-        </is>
-      </c>
       <c r="AU14" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AV14" s="3" t="inlineStr">
@@ -3430,7 +3428,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3448,17 +3446,17 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26益阳01</t>
+          <t>26苏州高新MTN008</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>520452.SZ</t>
+          <t>102683522.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3467,55 +3465,55 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>57.72</v>
+        <v>34.47</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>19益阳01</t>
+          <t>24苏州高新MTN007B</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>114D</t>
+          <t>2.93Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.5990</t>
+          <t>1.7448</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.6100/--</t>
+          <t>1.7600/1.7000</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>益阳市城市建设投资运营集团有限责任公司</t>
+          <t>苏州苏高新集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 14.57</t>
+          <t>C- 22.62</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3525,7 +3523,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3535,52 +3533,50 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="V15" s="3"/>
+        <v>8.1</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>1.375</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>2.05%~2.15%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>湖南省-益阳市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,公司拟将本期债券募集资金全部用于偿还公司债券本金或置换偿还公司债券本金的自有资金[23益阳01]</t>
+          <t>发行人本次发行金额3亿元债务融资工具,全部用于偿还到期有息债务[23苏州高新MTN004]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>益阳市发展投资集团有限公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3590,93 +3586,93 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>益阳市城市建设投资运营集团有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>苏州苏高新集团有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN15" s="3" t="inlineStr">
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY15" s="3" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AO15" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ15" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR15" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX15" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ15" s="3"/>
@@ -3684,7 +3680,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26国金集团MTN001(并购)</t>
+          <t>26国金集团SCP001</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3694,30 +3690,30 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683516.IB</t>
+          <t>012682197.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 1.85</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9.61</v>
+        <v>12.12</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -3767,7 +3763,7 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="V16" s="4" t="n">
         <v>1.0</v>
@@ -3779,7 +3775,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.58%~1.62%</t>
         </is>
       </c>
       <c r="Y16" s="3"/>
@@ -3791,18 +3787,18 @@
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期并购票据发行规模为20亿元,全部用于偿还发行人金融机构借款(并购贷款)</t>
+          <t>本次募集资金50,000.00万元用于偿还银行贷款7,804.20万元、购买固定资产及装修36,895.80万元、购买软硬件设施5,300.00万元</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3817,7 +3813,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>江苏省国金投资集团有限公司2026年度第一期中期票据(并购)</t>
+          <t>江苏省国金投资集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3827,7 +3823,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-03</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3874,7 +3870,7 @@
       </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AV16" s="3" t="inlineStr">
@@ -3884,7 +3880,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3902,74 +3898,74 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26苏州高新MTN008</t>
+          <t>26中交租赁SCP005</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683522.IB</t>
+          <t>012682196.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>34.47</v>
+        <v>17.12</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>24苏州高新MTN007B</t>
+          <t>24交租V1</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>278D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.7448</t>
+          <t>1.5683</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7000</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>苏州苏高新集团有限公司</t>
+          <t>中交融资租赁有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 22.62</t>
+          <t>C- 12.16</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3989,23 +3985,23 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>8.1</v>
+        <v>3.3833</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.375</v>
+        <v>1.0</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.53%~1.57%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4016,28 +4012,28 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行金额3亿元债务融资工具,全部用于偿还到期有息债务[23苏州高新MTN004]</t>
+          <t>本期超短期融资券拟募集资金6亿元,拟全部用于偿还发行人即将到期的债务融资工具[26中交租赁SCP003]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>上海银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4047,7 +4043,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>苏州苏高新集团有限公司2026年度第八期中期票据</t>
+          <t>中交融资租赁有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4057,13 +4053,13 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
@@ -4073,37 +4069,37 @@
       </c>
       <c r="AN17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4128,7 +4124,7 @@
       </c>
       <c r="AY17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ17" s="3"/>
@@ -4136,7 +4132,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26国金集团SCP001</t>
+          <t>26南海农商行绿债01B</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4146,120 +4142,132 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>012682197.IB</t>
+          <t>222680020.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12.12</v>
+        <v>48.72</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>25南海农商行债01</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>2.18Y</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>1.6179</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>1.6300/--</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>广东南海农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>A- 61.67</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>09-02 09:00</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>江苏省国金投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>C+ 35.00</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>09-02 09:00</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.62%</t>
-        </is>
-      </c>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金50,000.00万元用于偿还银行贷款7,804.20万元、购买固定资产及装修36,895.80万元、购买软硬件设施5,300.00万元</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,江苏银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4269,7 +4277,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>江苏省国金投资集团有限公司2026年度第一期超短期融资券</t>
+          <t>广东南海农村商业银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4279,49 +4287,53 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>金融</t>
         </is>
       </c>
-      <c r="AP18" s="3"/>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4354,74 +4366,74 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26中交租赁SCP005</t>
+          <t>26泉州文旅MTN003</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>012682196.IB</t>
+          <t>102683478.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>6.0</v>
+        <v>2.5</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>17.12</v>
+        <v>44.47</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>24交租V1</t>
+          <t>24泉旅04</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>278D</t>
+          <t>3.14Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.5683</t>
+          <t>1.6876</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>1.7800/1.7000</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>中交融资租赁有限公司</t>
+          <t>泉州文化旅游发展集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 12.16</t>
+          <t>C 28.82</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4441,14 +4453,14 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.3833</v>
+        <v>4.62</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.0</v>
+        <v>1.71</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
@@ -4457,39 +4469,39 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.57%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟募集资金6亿元,拟全部用于偿还发行人即将到期的债务融资工具[26中交租赁SCP003]</t>
+          <t>发行人本期中期票据发行金额5亿元,拟全部用于偿还发行人存量债务融资工具本金[23泉州文旅MTN003]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,兴业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
@@ -4499,7 +4511,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>中交融资租赁有限公司2026年度第五期超短期融资券</t>
+          <t>泉州文化旅游发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4509,78 +4521,78 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY19" s="3" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>融资租赁</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX19" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ19" s="3"/>
@@ -4588,74 +4600,68 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26南海农商行绿债01B</t>
+          <t>26泉州文旅MTN003B(取消发行)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>222680020.IB</t>
+          <t>DY102683479.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>48.72</v>
-      </c>
+          <t>1.60 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>25南海农商行债01</t>
+          <t>26泉州文旅MTN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>4.60Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.6179</t>
+          <t>1.8302</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.6300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>广东南海农村商业银行股份有限公司</t>
+          <t>泉州文化旅游发展集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>A- 61.67</t>
+          <t>C 28.82</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4682,48 +4688,44 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
+          <t>发行人本期中期票据发行金额5亿元,拟全部用于偿还发行人存量债务融资工具本金[23泉州文旅MTN003]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4733,7 +4735,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>广东南海农村商业银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
+          <t>泉州文化旅游发展集团有限公司2026年度第三期中期票据(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4743,7 +4745,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4754,7 +4756,7 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
@@ -4764,32 +4766,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4814,7 +4816,7 @@
       </c>
       <c r="AY20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AZ20" s="3"/>
@@ -4822,17 +4824,17 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26泉州文旅MTN003</t>
+          <t>26曹国07</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683478.IB</t>
+          <t>245951.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4841,55 +4843,55 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.0</v>
+        <v>5.5</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>44.47</v>
+        <v>62.72</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>24泉旅04</t>
+          <t>24曹妃国控MTN004</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>3.14Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.6876</t>
+          <t>1.9241</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.7800/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>泉州文化旅游发展集团有限公司</t>
+          <t>曹妃甸国控投资集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C 28.82</t>
+          <t>C+ 34.05</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4899,7 +4901,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4913,46 +4915,48 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>1.71</v>
-      </c>
+        <v>3.87</v>
+      </c>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z21" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额5亿元,拟全部用于偿还发行人存量债务融资工具本金[23泉州文旅MTN003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4962,12 +4966,12 @@
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>泉州文化旅游发展集团有限公司2026年度第三期中期票据</t>
+          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4983,12 +4987,12 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN21" s="3" t="inlineStr">
@@ -4998,27 +5002,27 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
@@ -5048,7 +5052,7 @@
       </c>
       <c r="AY21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ21" s="3"/>
@@ -5056,17 +5060,17 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26泉州文旅MTN003B(取消发行)</t>
+          <t>26扬州03</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>DY102683479.IB</t>
+          <t>283768.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -5075,34 +5079,40 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>57.61</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26泉州文旅MTN001</t>
+          <t>26扬州02</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>4.60Y</t>
+          <t>4.64Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.8302</t>
+          <t>1.9555</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5112,12 +5122,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>泉州文化旅游发展集团有限公司</t>
+          <t>扬州广合国有资本运营集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C 28.82</t>
+          <t>C- 15.80</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5127,7 +5137,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5140,16 +5150,18 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>3.25</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5160,23 +5172,23 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额5亿元,拟全部用于偿还发行人存量债务融资工具本金[23泉州文旅MTN003]</t>
+          <t>本期债券发行规模为人民币6.00亿元整,本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金。[23扬州04]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5186,17 +5198,17 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>泉州文化旅游发展集团有限公司2026年度第三期中期票据(品种二)(取消发行)</t>
+          <t>扬州广合国有资本运营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
@@ -5207,12 +5219,12 @@
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
@@ -5222,7 +5234,7 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
@@ -5237,17 +5249,17 @@
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5272,7 +5284,7 @@
       </c>
       <c r="AY22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ22" s="3"/>
@@ -5280,7 +5292,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26曹国07</t>
+          <t>26菏财GT01</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5290,64 +5302,64 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>245951.SH</t>
+          <t>520445.SZ</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.5</v>
+        <v>2.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>62.72</v>
+        <v>49.61</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>24曹妃国控MTN004</t>
+          <t>26菏财01</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>2.65Y+2.00Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.9241</t>
+          <t>1.8637</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司</t>
+          <t>菏泽财金投资集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.05</t>
+          <t>B- 38.33</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5371,7 +5383,7 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>3.87</v>
+        <v>3.05</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
@@ -5381,32 +5393,28 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>山东省-菏泽市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的21曹国04本金[21曹国04]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,申万宏源证券有限公司,长城证券股份有限公司,德邦证券股份有限公司</t>
+          <t>国投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5422,22 +5430,22 @@
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>曹妃甸国控投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
+          <t>菏泽财金投资集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5458,7 +5466,7 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
@@ -5468,27 +5476,27 @@
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV23" s="3" t="inlineStr">
@@ -5498,7 +5506,7 @@
       </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX23" s="3" t="inlineStr">
@@ -5516,7 +5524,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26海创Y1</t>
+          <t>26珠华04</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5526,49 +5534,49 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>283897.SH</t>
+          <t>520444.SZ</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>2+2+1</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>56.72</v>
+        <v>134.61</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26海创02</t>
+          <t>25珠华02</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.60Y</t>
+          <t>2.21Y+2.00Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7200</t>
+          <t>2.8118</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5578,12 +5586,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>宁波海创集团有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>D- 0.86</t>
+          <t>B- 38.69</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5607,17 +5615,17 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.18</v>
+        <v>2.3</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>2.73%~2.83%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5628,17 +5636,17 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金。[23海创02]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于置换到期的公司债券本金[23珠华Y3]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>甬兴证券有限公司,华福证券股份有限公司</t>
+          <t>华金证券股份有限公司,国泰海通证券股份有限公司,西部证券股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,国信证券股份有限公司,中国银河证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5654,12 +5662,12 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>宁波海创集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+          <t>珠海华发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5669,13 +5677,13 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
@@ -5695,7 +5703,7 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
@@ -5705,12 +5713,12 @@
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
@@ -5720,7 +5728,7 @@
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5730,12 +5738,12 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY24" s="3" t="inlineStr">
@@ -5748,7 +5756,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26扬州03</t>
+          <t>26淮开06</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5758,64 +5766,64 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>283768.SH</t>
+          <t>283873.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.0</v>
+        <v>4.3</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.0</v>
+        <v>4.3</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>57.61</v>
+        <v>40.47</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26扬州02</t>
+          <t>26淮开04</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.64Y</t>
+          <t>1.96Y+3.00Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.9555</t>
+          <t>1.7086</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>扬州广合国有资本运营集团有限公司</t>
+          <t>淮安开发控股有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 15.80</t>
+          <t>C- 24.53</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5825,7 +5833,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5839,17 +5847,17 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5860,17 +5868,17 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为人民币6.00亿元整,本期债券募集资金扣除发行费用后,全部用于偿还到期公司债券本金。[23扬州04]</t>
+          <t>本期债券的募集资金扣除发行费用后拟用于偿还发行人公司债券本金[23淮开05]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>国信证券股份有限公司,国金证券股份有限公司,中国银河证券股份有限公司,中邮证券有限责任公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5891,7 +5899,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>扬州广合国有资本运营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>淮安开发控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5901,13 +5909,13 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2030-09-04</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -5937,12 +5945,12 @@
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
@@ -5952,7 +5960,7 @@
       </c>
       <c r="AU25" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AV25" s="3" t="inlineStr">
@@ -5962,7 +5970,7 @@
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
@@ -5980,7 +5988,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26三能K1</t>
+          <t>26怀科01</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5990,64 +5998,64 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>245905.SH</t>
+          <t>283753.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>34.39</v>
+        <v>37.61</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24三峡新能MTN002</t>
+          <t>26怀柔科学PPN002</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>7.76Y</t>
+          <t>2.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.9466</t>
+          <t>1.7591</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.9700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>中国三峡新能源(集团)股份有限公司</t>
+          <t>北京怀柔科学城建设发展有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 15.38</t>
+          <t>C- 23.93</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6071,17 +6079,17 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>4.22</v>
+        <v>3.13</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6096,17 +6104,17 @@
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>北京市-怀柔区</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后拟全部用于生产性支出,包括偿还公司有息债务、补充流动资金、项目建设及运营等符合法律法规规定的用途。</t>
+          <t>本期公司债券募集资金拟用于偿还到期的公司债券[23怀科01]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,平安证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6117,7 +6125,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -6127,17 +6135,17 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>中国三峡新能源(集团)股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2036-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
@@ -6158,37 +6166,37 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV26" s="3" t="inlineStr">
@@ -6198,7 +6206,7 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -6216,7 +6224,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26菏财GT01</t>
+          <t>26沂投03</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6226,64 +6234,64 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>520445.SZ</t>
+          <t>283864.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.0</v>
+        <v>5.9</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>49.61</v>
+        <v>57.72</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26菏财01</t>
+          <t>26沂投02</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.65Y+2.00Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.8637</t>
+          <t>1.8701</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>1.8900/1.8700</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>菏泽财金投资集团有限公司</t>
+          <t>新沂市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 38.33</t>
+          <t>C 26.13</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6303,45 +6311,49 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.05</v>
+        <v>4.1525</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>山东省-菏泽市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23沂投05]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD27" s="3"/>
+          <t>国金证券股份有限公司,天风证券股份有限公司,国投证券股份有限公司,南京证券股份有限公司,兴业证券股份有限公司,东兴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>江苏钟吾城乡投资发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE27" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -6354,12 +6366,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>菏泽财金投资集团有限公司2026年面向专业投资者非公开发行低碳转型挂钩公司债券(第一期)(品种一)</t>
+          <t>新沂市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6369,68 +6381,68 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AO27" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ27" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR27" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>一般零售</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-04</t>
-        </is>
-      </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6448,59 +6460,59 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26珠华04</t>
+          <t>26厦门银行债01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>520444.SZ</t>
+          <t>212680031.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2+2+1</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.75</v>
+        <v>1.59</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>134.61</v>
+        <v>33.72</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25珠华02</t>
+          <t>25厦门银行科创债01(柜台)</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.21Y+2.00Y</t>
+          <t>4.03Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2.8118</t>
+          <t>1.6337</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6510,12 +6522,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司</t>
+          <t>厦门银行股份有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 38.69</t>
+          <t>A- 60.10</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6525,7 +6537,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6538,18 +6550,16 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U28" s="4" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.73%~2.83%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6560,101 +6570,101 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于置换到期的公司债券本金[23珠华Y3]</t>
+          <t>用于优化发行人负债结构，充实营运资金，促进业务稳健发展，优先用于支持科技创新领域信贷投放，其中重点支持专精特新企业，加大对科技创新的支持力度。</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司,国泰海通证券股份有限公司,西部证券股份有限公司,中信建投证券股份有限公司,光大证券股份有限公司,国信证券股份有限公司,中国银河证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,国开证券股份有限公司,中国银行股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,交通银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>珠海华发集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>厦门银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AO28" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t>2028-09-04</t>
-        </is>
-      </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6662,7 +6672,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6680,74 +6690,74 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26淮开06</t>
+          <t>26酒钢MTN003</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>283873.SH</t>
+          <t>102683525.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2+2</t>
+          <t>2+N</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.3</v>
+        <v>5.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.3</v>
+        <v>5.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.70 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>40.47</v>
+        <v>61.41</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26淮开04</t>
+          <t>25酒钢MTN001(科创债)</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>1.96Y+3.00Y</t>
+          <t>2.06Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7086</t>
+          <t>1.8257</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>淮安开发控股有限公司</t>
+          <t>酒泉钢铁(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 24.53</t>
+          <t>C- 17.50</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6757,7 +6767,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6771,9 +6781,11 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V29" s="3"/>
+        <v>2.64</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>3.25</v>
+      </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
           <t>7+</t>
@@ -6781,34 +6793,34 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>甘肃省-嘉峪关市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后拟用于偿还发行人公司债券本金[23淮开05]</t>
+          <t>本期永续中期票据发行拟募集资金5亿元,所募集资金拟用于归还金融机构贷款及支付氧化铝货款。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,国金证券股份有限公司,中国银河证券股份有限公司,中邮证券有限责任公司</t>
+          <t>上海浦东发展银行股份有限公司,东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6818,33 +6830,33 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>淮安开发控股有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>酒泉钢铁(集团)有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2030-09-04</t>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6854,37 +6866,37 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6894,92 +6906,94 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AZ29" s="3"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AZ29" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26怀科01</t>
+          <t>26南海农商行绿债01A</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283753.SH</t>
+          <t>222680019.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>37.61</v>
+        <v>37.72</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26怀柔科学PPN002</t>
+          <t>25南海农商行债01</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+2.00Y</t>
+          <t>2.18Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7591</t>
+          <t>1.6179</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6300/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司</t>
+          <t>广东南海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 23.93</t>
+          <t>A- 61.67</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6989,7 +7003,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -7002,18 +7016,16 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U30" s="4" t="n">
-        <v>3.13</v>
-      </c>
+      <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7028,59 +7040,59 @@
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>北京市-怀柔区</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于偿还到期的公司债券[23怀科01]</t>
+          <t>发行人本次拟发行规模不超过8亿元人民币的绿色金融债券,募集资金拟投向符合《绿色金融支持项目目录(2025年版)》标准的绿色储备项目共9项,项目拟使用绿色债券募集资金8.40亿元人民币。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>广东南海农村商业银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -7090,37 +7102,37 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV30" s="3" t="inlineStr">
@@ -7130,7 +7142,7 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7148,7 +7160,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26怀科02</t>
+          <t>26运河01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7158,64 +7170,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283754.SH</t>
+          <t>283877.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>41.95</v>
+        <v>55.61</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24怀科03</t>
+          <t>24古运河PPN001</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>3.18Y</t>
+          <t>1.22Y+2.00Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7890</t>
+          <t>1.7878</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.7700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司</t>
+          <t>江苏古运河投资集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 23.93</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7225,7 +7237,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-02 16:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7239,45 +7251,45 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.27</v>
+        <v>4.58</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>北京市-怀柔区</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于偿还到期的公司债券。[23怀科01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券本金,或置换自有资金偿还的公司债券本金。[23运河01]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD31" s="3"/>
+          <t>天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>无锡市城南建设投资发展有限公司</t>
+        </is>
+      </c>
       <c r="AE31" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7295,7 +7307,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>江苏古运河投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7305,14 +7317,10 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2033-09-04</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-04</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
@@ -7320,7 +7328,7 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7330,12 +7338,12 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
@@ -7345,12 +7353,12 @@
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
@@ -7360,17 +7368,17 @@
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7388,7 +7396,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26沂投03</t>
+          <t>26海创Y1</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7398,19 +7406,19 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>283864.SH</t>
+          <t>283897.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.9</v>
+        <v>6.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.9</v>
+        <v>6.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -7418,44 +7426,44 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>57.72</v>
+        <v>56.72</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26沂投02</t>
+          <t>26海创02</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>2.60Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.8701</t>
+          <t>1.7200</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.8900/1.8700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>新沂市城市投资发展集团有限公司</t>
+          <t>宁波海创集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C 26.13</t>
+          <t>D- 0.86</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7475,49 +7483,45 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.1525</v>
+        <v>3.18</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23沂投05]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金。[23海创02]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,天风证券股份有限公司,国投证券股份有限公司,南京证券股份有限公司,兴业证券股份有限公司,东兴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD32" s="3" t="inlineStr">
-        <is>
-          <t>江苏钟吾城乡投资发展集团有限公司</t>
-        </is>
-      </c>
+          <t>甬兴证券有限公司,华福证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>新沂市城市投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>宁波海创集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7545,13 +7549,13 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
@@ -7561,17 +7565,17 @@
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
@@ -7581,17 +7585,17 @@
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7601,17 +7605,17 @@
       </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY32" s="3" t="inlineStr">
@@ -7624,86 +7628,86 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26厦门银行债01</t>
+          <t>26怀科02</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>09-02 19:00</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>283754.SH</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>5+2</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>24怀科03</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>3.18Y</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>1.7890</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>北京怀柔科学城建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>C- 23.93</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
           <t>09-02 16:00</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>212680031.IB</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>3Y</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>1.30 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>33.72</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>25厦门银行科创债01(柜台)</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>4.03Y</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>1.6337</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>厦门银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>A- 60.10</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>09-02 09:00</t>
-        </is>
-      </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -7714,16 +7718,18 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U33" s="3"/>
+      <c r="U33" s="4" t="n">
+        <v>2.27</v>
+      </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7731,57 +7737,65 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z33" s="3"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>北京市-怀柔区</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>用于优化发行人负债结构，充实营运资金，促进业务稳健发展，优先用于支持科技创新领域信贷投放，其中重点支持专精特新企业，加大对科技创新的支持力度。</t>
+          <t>本期公司债券募集资金拟用于偿还到期的公司债券。[23怀科01]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,国开证券股份有限公司,中国银行股份有限公司,中国国际金融股份有限公司,兴业银行股份有限公司,交通银行股份有限公司,申万宏源证券有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>厦门银行股份有限公司2026年第一期金融债券</t>
+          <t>北京怀柔科学城建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2033-09-04</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
@@ -7796,37 +7810,37 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AV33" s="3" t="inlineStr">
@@ -7836,7 +7850,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7854,59 +7868,59 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26酒钢MTN003</t>
+          <t>26绵控05</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>102683525.IB</t>
+          <t>283898.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>2+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>61.41</v>
+        <v>62.61</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25酒钢MTN001(科创债)</t>
+          <t>26绵控04</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.06Y</t>
+          <t>4.81Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.8257</t>
+          <t>2.0201</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7916,12 +7930,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>酒泉钢铁(集团)有限责任公司</t>
+          <t>绵阳市投资控股(集团)有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 17.50</t>
+          <t>C- 19.14</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7931,7 +7945,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7941,50 +7955,48 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V34" s="4" t="n">
         <v>3.25</v>
       </c>
+      <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.98%~2.08%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>甘肃省-嘉峪关市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期永续中期票据发行拟募集资金5亿元,所募集资金拟用于归还金融机构贷款及支付氧化铝货款。</t>
+          <t>本期债券的募集资金将用于偿还回售或到期的公司债券本金[23绵控06]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,东兴证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,西部证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7994,28 +8006,28 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>酒泉钢铁(集团)有限责任公司2026年度第三期中期票据</t>
+          <t>绵阳市投资控股(集团)有限公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2031-09-03</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -8025,37 +8037,37 @@
       </c>
       <c r="AN34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8070,94 +8082,92 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AZ34" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AZ34" s="3"/>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26南海农商行绿债01A</t>
+          <t>26三能K1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>222680019.IB</t>
+          <t>245905.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.63</v>
+        <v>2.03</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>37.72</v>
+        <v>34.39</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>25南海农商行债01</t>
+          <t>24三峡新能MTN002</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.18Y</t>
+          <t>7.76Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6179</t>
+          <t>1.9466</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.6300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>广东南海农村商业银行股份有限公司</t>
+          <t>中国三峡新能源(集团)股份有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>A- 61.67</t>
+          <t>C- 15.38</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8167,7 +8177,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8180,16 +8190,18 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U35" s="3"/>
+      <c r="U35" s="4" t="n">
+        <v>4.22</v>
+      </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8204,38 +8216,38 @@
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本次拟发行规模不超过8亿元人民币的绿色金融债券,募集资金拟投向符合《绿色金融支持项目目录(2025年版)》标准的绿色储备项目共9项,项目拟使用绿色债券募集资金8.40亿元人民币。</t>
+          <t>本期债券的募集资金扣除发行费用后拟全部用于生产性支出,包括偿还公司有息债务、补充流动资金、项目建设及运营等符合法律法规规定的用途。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>广东南海农村商业银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
+          <t>中国三峡新能源(集团)股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8245,18 +8257,18 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2036-09-04</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
@@ -8266,32 +8278,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -12294,59 +12306,59 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26绵控05</t>
+          <t>26台州科创PPN001</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>283898.SH</t>
+          <t>032680510.IB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>17.0</v>
+        <v>6.0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>17.0</v>
+        <v>6.0</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>62.61</v>
+        <v>43.72</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26绵控04</t>
+          <t>26台创02</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>4.81Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>2.0201</t>
+          <t>1.6885</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -12356,12 +12368,12 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>绵阳市投资控股(集团)有限公司</t>
+          <t>台州市科创投资集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 19.14</t>
+          <t>C 26.25</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12371,7 +12383,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 14:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -12385,44 +12397,46 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V53" s="3"/>
+        <v>4.4</v>
+      </c>
+      <c r="V53" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.98%~2.08%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>浙江省-台州市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将用于偿还回售或到期的公司债券本金[23绵控06]</t>
+          <t>本期定向债务融资工具发行金额6.00亿元,募集资金拟全部用于偿还到期的债务融资工具本金[23台州金投PPN001]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,西部证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>东方证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
@@ -12432,12 +12446,12 @@
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>绵阳市投资控股(集团)有限公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
+          <t>台州市科创投资集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12447,18 +12461,18 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2031-09-03</t>
+          <t>2029-09-03</t>
         </is>
       </c>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AM53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN53" s="3" t="inlineStr">
@@ -12468,12 +12482,12 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
@@ -12493,7 +12507,7 @@
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
@@ -12526,7 +12540,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26台州科创PPN001</t>
+          <t>26临平交通PPN004</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12536,64 +12550,64 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>032680510.IB</t>
+          <t>032680513.IB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>43.72</v>
+        <v>34.61</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26台创02</t>
+          <t>26临交01</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>2.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.6885</t>
+          <t>1.7538</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/--</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>台州市科创投资集团有限公司</t>
+          <t>杭州临平交通集团有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C 26.25</t>
+          <t>B- 43.05</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12603,7 +12617,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>09-02 14:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -12613,44 +12627,44 @@
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>浙江省-台州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额6.00亿元,募集资金拟全部用于偿还到期的债务融资工具本金[23台州金投PPN001]</t>
+          <t>本期发行金额人民币10亿元,拟用于偿还发行人本部有息债务[23临平交通PPN003]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>宁波银行股份有限公司,兴业银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
@@ -12671,7 +12685,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>台州市科创投资集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>杭州临平交通集团有限公司2026年度第四期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12681,33 +12695,33 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2029-09-03</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK54" s="3"/>
       <c r="AL54" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AM54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
@@ -12727,12 +12741,12 @@
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AV54" s="3" t="inlineStr">
@@ -12742,7 +12756,7 @@
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX54" s="3" t="inlineStr">
@@ -12760,22 +12774,22 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26临平交通PPN004</t>
+          <t>26远东租赁MTN008</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-03 18:00</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>032680513.IB</t>
+          <t>102683520.IB</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
@@ -12786,48 +12800,48 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.71 ~ 1.91</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>34.61</v>
+        <v>67.41</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26临交01</t>
+          <t>25远东六</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+2.00Y</t>
+          <t>1.98Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.7538</t>
+          <t>1.9400</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1.7700/--</t>
+          <t>--/1.8800</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>杭州临平交通集团有限公司</t>
+          <t>远东国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>B- 43.05</t>
+          <t>C- 23.08</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12851,46 +12865,44 @@
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V55" s="4" t="n">
-        <v>1.25</v>
-      </c>
+        <v>0.58</v>
+      </c>
+      <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额人民币10亿元,拟用于偿还发行人本部有息债务[23临平交通PPN003]</t>
+          <t>本期债务融资工具拟募集资金10.00亿元，5.00亿元用于偿还发行人即将到期的债务融资工具，5.00亿元用于偿还发行人及子公司金融机构借款[24远东租赁MTN006]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,兴业银行股份有限公司,杭州银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF55" s="3" t="inlineStr">
@@ -12905,17 +12917,17 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>杭州临平交通集团有限公司2026年度第四期定向债务融资工具</t>
+          <t>远东国际融资租赁有限公司2026年度第八期中期票据</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AK55" s="3"/>
@@ -12926,7 +12938,7 @@
       </c>
       <c r="AM55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN55" s="3" t="inlineStr">
@@ -12936,37 +12948,37 @@
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t/>
         </is>
       </c>
       <c r="AV55" s="3" t="inlineStr">
@@ -12976,7 +12988,7 @@
       </c>
       <c r="AW55" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX55" s="3" t="inlineStr">
@@ -12986,15 +12998,17 @@
       </c>
       <c r="AY55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="AZ55" s="3"/>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AZ55" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26远东租赁MTN008</t>
+          <t>26广西路建MTN002</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -13004,64 +13018,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>102683520.IB</t>
+          <t>102683524.IB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.71 ~ 1.91</t>
+          <t>1.75 ~ 2.10</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>67.41</v>
+        <v>45.61</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>25远东六</t>
+          <t>25广西路建MTN002(科创债)</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>1.98Y</t>
+          <t>4.18Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.9400</t>
+          <t>2.0250</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>--/1.8800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>远东国际融资租赁有限公司</t>
+          <t>广西路建工程集团有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C- 23.08</t>
+          <t>D+ 5.45</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13085,38 +13099,40 @@
         </is>
       </c>
       <c r="U56" s="4" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="V56" s="3"/>
+        <v>2.6667</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.91%~2.01%</t>
+          <t>2.01%~2.11%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具拟募集资金10.00亿元，5.00亿元用于偿还发行人即将到期的债务融资工具，5.00亿元用于偿还发行人及子公司金融机构借款[24远东租赁MTN006]</t>
+          <t>本期中期票据募集资金3亿元,全部用于偿还到期银行借款</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,天津银行股份有限公司</t>
+          <t>中信银行股份有限公司,广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
@@ -13137,7 +13153,7 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>远东国际融资租赁有限公司2026年度第八期中期票据</t>
+          <t>广西路建工程集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -13147,7 +13163,7 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2031-09-04</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
@@ -13158,7 +13174,7 @@
       </c>
       <c r="AM56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN56" s="3" t="inlineStr">
@@ -13168,32 +13184,32 @@
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -13221,14 +13237,12 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AZ56" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ56" s="3"/>
     </row>
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26广西路建MTN002</t>
+          <t>26海螺科创MTN001</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -13238,7 +13252,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>102683524.IB</t>
+          <t>102683526.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -13247,55 +13261,55 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.75 ~ 2.10</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>45.61</v>
+        <v>22.61</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>25广西路建MTN002(科创债)</t>
+          <t>26康达新材MTN001(科创债)</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>4.18Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>2.0250</t>
+          <t>2.9310</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.8300</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>广西路建工程集团有限公司</t>
+          <t>安徽海螺科创材料有限责任公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.45</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13305,7 +13319,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 10:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -13319,19 +13333,19 @@
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>2.6667</v>
+        <v>4.98</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>5.0</v>
+        <v>2.08</v>
       </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>2.01%~2.11%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -13339,23 +13353,31 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z57" s="3"/>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金3亿元,全部用于偿还到期银行借款</t>
+          <t>发行人本次中期票据计划注册30亿元，其中15亿元用于偿还发行人及合并报表范围内子公司有息负债，15亿元用于补流。首期发行10亿元，其中7.4亿元用于偿还发行人及合并报表范围内子公司有息负债，2.6亿元用于补流</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,广西北部湾银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD57" s="3"/>
+          <t>兴业银行股份有限公司,徽商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr">
+        <is>
+          <t>安徽海螺集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE57" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -13373,7 +13395,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>广西路建工程集团有限公司2026年度第二期中期票据</t>
+          <t>安徽海螺科创材料有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13407,29 +13429,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="AP57" s="3"/>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
@@ -13439,7 +13457,7 @@
       </c>
       <c r="AV57" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW57" s="3" t="inlineStr">
@@ -13462,74 +13480,74 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26海螺科创MTN001</t>
+          <t>26国耀04</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>09-03 18:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>102683526.IB</t>
+          <t>245990.SH</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>22.61</v>
+        <v>53.11</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26康达新材MTN001(科创债)</t>
+          <t>25国耀融汇MTN002</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>2.04Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>2.9310</t>
+          <t>1.8676</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>--/2.8300</t>
+          <t>--/1.8200</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺科创材料有限责任公司</t>
+          <t>国耀融汇融资租赁有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>C- 19.74</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13539,7 +13557,7 @@
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>09-02 10:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -13553,69 +13571,59 @@
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="V58" s="4" t="n">
-        <v>2.08</v>
-      </c>
+        <v>3.01</v>
+      </c>
+      <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z58" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据计划注册30亿元，其中15亿元用于偿还发行人及合并报表范围内子公司有息负债，15亿元用于补流。首期发行10亿元，其中7.4亿元用于偿还发行人及合并报表范围内子公司有息负债，2.6亿元用于补流</t>
+          <t>本期债券募集资金不超过6.00亿元用于偿还有息债务,剩余部分用于补充公司融资租赁业务、保理业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出[24控租03]</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,徽商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD58" s="3" t="inlineStr">
-        <is>
-          <t>安徽海螺集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG58" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺科创材料有限责任公司2026年度第一期中期票据</t>
+          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13625,18 +13633,18 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-09-04</t>
+          <t>2028-09-04</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
       <c r="AL58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t/>
         </is>
       </c>
       <c r="AM58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN58" s="3" t="inlineStr">
@@ -13646,28 +13654,32 @@
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP58" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -13677,7 +13689,7 @@
       </c>
       <c r="AV58" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW58" s="3" t="inlineStr">
@@ -13692,7 +13704,7 @@
       </c>
       <c r="AY58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AZ58" s="3"/>
@@ -13700,7 +13712,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26国耀04</t>
+          <t>26建邺01</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13710,64 +13722,64 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>245990.SH</t>
+          <t>283862.SH</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>53.11</v>
+        <v>49.72</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>25国耀融汇MTN002</t>
+          <t>26建邺K2</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2.04Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.8676</t>
+          <t>1.6902</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/1.8200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>国耀融汇融资租赁有限公司</t>
+          <t>南京市建邺区高新科技投资集团有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 19.74</t>
+          <t>C- 12.86</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13791,38 +13803,38 @@
         </is>
       </c>
       <c r="U59" s="4" t="n">
-        <v>3.01</v>
+        <v>6.38</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过6.00亿元用于偿还有息债务,剩余部分用于补充公司融资租赁业务、保理业务等日常生产经营所需流动资金,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出[24控租03]</t>
+          <t>本期债券募集资金40,000.00万元拟全部用于置换回售公司债券发行人支付的自有资金[GC建邺01]</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,华泰联合证券有限责任公司</t>
+          <t>华泰联合证券有限责任公司,南京证券股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
@@ -13833,7 +13845,7 @@
       </c>
       <c r="AF59" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG59" s="3" t="inlineStr">
@@ -13843,23 +13855,23 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>国耀融汇融资租赁有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>南京市建邺区高新科技投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2028-09-04</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
       <c r="AL59" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM59" s="3" t="inlineStr">
@@ -13874,32 +13886,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13932,74 +13944,74 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26建邺01</t>
+          <t>26京东PPN002</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>09-02 19:00</t>
+          <t>09-02 18:00</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>283862.SH</t>
+          <t>032680509.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>4.0</v>
+        <v>40.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>4.0</v>
+        <v>40.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>49.72</v>
+        <v>19.5</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26建邺K2</t>
+          <t>26京东PPN001</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>76D</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.6902</t>
+          <t>1.5120</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>南京市建邺区高新科技投资集团有限公司</t>
+          <t>北京京东世纪贸易有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 12.86</t>
+          <t>C- 11.41</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14009,7 +14021,7 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 09:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -14023,59 +14035,61 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="V60" s="3"/>
+        <v>3.7375</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>2.05</v>
+      </c>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.63%~1.67%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金40,000.00万元拟全部用于置换回售公司债券发行人支付的自有资金[GC建邺01]</t>
+          <t>本期定向工具基础发行规模为0亿元，发行金额上限40亿元，募集资金用于偿还公司有息借款、银行承兑汇票及补充公司流动资金</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,南京证券股份有限公司</t>
+          <t>中国农业银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
       <c r="AE60" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF60" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG60" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>南京市建邺区高新科技投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>北京京东世纪贸易有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14085,13 +14099,13 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AM60" s="3" t="inlineStr">
@@ -14106,32 +14120,32 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>线上零售</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>线上零售</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14164,74 +14178,74 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26京东PPN002</t>
+          <t>26渤海银行债01</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>09-02 18:00</t>
+          <t>09-02 17:00</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>032680509.IB</t>
+          <t>212680029.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>40.0</v>
+        <v>100.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>40.0</v>
+        <v>150.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>19.5</v>
+        <v>34.72</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26京东PPN001</t>
+          <t>25渤海银行债02A</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>76D</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.5120</t>
+          <t>1.6002</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>1.6100/--</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>北京京东世纪贸易有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C- 11.41</t>
+          <t>A 75.65</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14254,20 +14268,16 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U61" s="4" t="n">
-        <v>3.7375</v>
-      </c>
-      <c r="V61" s="4" t="n">
-        <v>2.05</v>
-      </c>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.67%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
@@ -14275,31 +14285,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z61" s="3"/>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期定向工具基础发行规模为0亿元，发行金额上限40亿元，募集资金用于偿还公司有息借款、银行承兑汇票及补充公司流动资金</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源 ，优化负债期限结构 ，促进业务的稳健发展 。</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中国银行股份有限公司,中信银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,华夏银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,国投证券股份有限公司,国开证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG61" s="3" t="inlineStr">
@@ -14309,17 +14323,17 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>北京京东世纪贸易有限公司2026年度第二期定向债务融资工具</t>
+          <t>渤海银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2027-06-01</t>
+          <t>2029-09-04</t>
         </is>
       </c>
       <c r="AK61" s="3"/>
@@ -14330,7 +14344,7 @@
       </c>
       <c r="AM61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AN61" s="3" t="inlineStr">
@@ -14340,7 +14354,7 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
@@ -14350,22 +14364,22 @@
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>线上零售</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>线上零售</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -14398,74 +14412,74 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26渤海银行债01</t>
+          <t>26深投07</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>09-02 17:00</t>
+          <t>09-02 19:00</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>212680029.IB</t>
+          <t>524987.SZ</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>150.0</v>
+        <v>5.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>34.72</v>
+        <v>33.61</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>25渤海银行债02A</t>
+          <t>26深投03</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>4.80Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.6002</t>
+          <t>1.7592</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>1.6100/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>深圳市投资控股有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>A 75.65</t>
+          <t>C- 19.95</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14475,7 +14489,7 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>09-02 09:00</t>
+          <t>09-02 15:00</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
@@ -14485,19 +14499,21 @@
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="U62" s="3"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>5.18</v>
+      </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
@@ -14512,23 +14528,23 @@
       </c>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源 ，优化负债期限结构 ，促进业务的稳健发展 。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国建设银行股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,华夏银行股份有限公司,兴业银行股份有限公司,浙商银行股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,国投证券股份有限公司,国开证券股份有限公司,东方证券股份有限公司</t>
+          <t>国信证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
@@ -14538,12 +14554,12 @@
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司2026年金融债券(第一期)</t>
+          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种一)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14553,53 +14569,57 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2029-09-04</t>
-        </is>
-      </c>
-      <c r="AK62" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK62" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL62" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AM62" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14632,7 +14652,7 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26深投07</t>
+          <t>26深投08</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14642,12 +14662,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>524987.SZ</t>
+          <t>524988.SZ</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
@@ -14658,38 +14678,38 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>33.61</v>
+        <v>39.39</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26深投03</t>
+          <t>26深投控MTN004B</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>4.80Y</t>
+          <t>9.89Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.7592</t>
+          <t>2.1167</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>2.1300/--</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
@@ -14723,7 +14743,7 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>5.18</v>
+        <v>6.0</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
@@ -14733,7 +14753,7 @@
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
@@ -14779,7 +14799,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种一)</t>
+          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14789,7 +14809,7 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t>2036-09-07</t>
         </is>
       </c>
       <c r="AK63" s="3" t="inlineStr">
@@ -14872,7 +14892,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26深投08</t>
+          <t>26九国04</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14882,64 +14902,64 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>524988.SZ</t>
+          <t>283891.SH</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>39.39</v>
+        <v>49.72</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26深投控MTN004B</t>
+          <t>26九国03</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>9.89Y</t>
+          <t>2.89Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>2.1167</t>
+          <t>1.7565</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>2.1300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司</t>
+          <t>九江市国有投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C- 19.95</t>
+          <t>B- 42.60</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14949,7 +14969,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>09-02 15:00</t>
+          <t>09-02 16:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -14959,21 +14979,21 @@
       </c>
       <c r="T64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>6.0</v>
+        <v>4.16</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -14981,24 +15001,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z64" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江西省-九江市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还存量公司债券[23深投05]</t>
+          <t>本期债券所募资金金额不超过10亿元（含10亿元），扣除发行费用后，用于偿还公司债券本金【23 九国V2】</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司,华泰联合证券有限责任公司,光大证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
@@ -15014,72 +15030,56 @@
       </c>
       <c r="AG64" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>深圳市投资控股有限公司2026年面向专业投资者公开发行公司债券(第四期)(品种二)</t>
+          <t>九江市国有投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2036-09-07</t>
-        </is>
-      </c>
-      <c r="AK64" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-04</t>
+        </is>
+      </c>
+      <c r="AK64" s="3"/>
       <c r="AL64" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AN64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ64" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR64" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS64" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3"/>
+      <c r="AR64" s="3"/>
+      <c r="AS64" s="3"/>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
